--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Reservas.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Reservas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD6DDC3-2D2A-4D57-99CE-0B7BFB9E392F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6481F5-058C-441A-970B-7770EB768B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="3" xr2:uid="{9E75F319-B909-453D-9AFC-FA9C5B40B20E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{9E75F319-B909-453D-9AFC-FA9C5B40B20E}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" r:id="rId1"/>
@@ -1328,7 +1328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="249">
   <si>
     <t>Tipo Objeto Dominio</t>
   </si>
@@ -1390,9 +1390,6 @@
     <t>Agendas</t>
   </si>
   <si>
-    <t>Agenda</t>
-  </si>
-  <si>
     <t>Turno</t>
   </si>
   <si>
@@ -1525,27 +1522,15 @@
     <t>Sólo números enteros</t>
   </si>
   <si>
-    <t xml:space="preserve">Sólo un valor lógico Si/No. </t>
-  </si>
-  <si>
-    <t>Sólo letras y espacios.</t>
-  </si>
-  <si>
     <t>xxxxxxxx-xxxx-xxxx-xxxx-xxxxxxxxxxxx, donde cada x representa un dígito del 0 al 9 o una letra de la "A" a la "F".</t>
   </si>
   <si>
-    <t>dd/MM/aaaa HH:MM dónde dd representa el día, MM representa el mes, aaaa, representa el año, HH representa la hora en formato de 24 horas, MM representa los minutos.</t>
-  </si>
-  <si>
     <t>horaInicio</t>
   </si>
   <si>
     <t>horaFin</t>
   </si>
   <si>
-    <t>agenda</t>
-  </si>
-  <si>
     <t xml:space="preserve">agenda </t>
   </si>
   <si>
@@ -1558,9 +1543,6 @@
     <t>numeroTurno</t>
   </si>
   <si>
-    <t>estado</t>
-  </si>
-  <si>
     <t>Es un dato que hace que cada turno sea único.</t>
   </si>
   <si>
@@ -1576,9 +1558,6 @@
     <t>Este dato es de tipo logico el cual dice si esta disponible o no disponible un turno</t>
   </si>
   <si>
-    <t>Este dato representa con que agenda está relacionada el turno.</t>
-  </si>
-  <si>
     <t>Reserva</t>
   </si>
   <si>
@@ -1903,9 +1882,6 @@
     <t>Detengo el proceso hasta que se ingresen datos valido para la creación de la reserva.</t>
   </si>
   <si>
-    <t>Filtro {Agenda.identificador}/Listar {Agenda.nombre}</t>
-  </si>
-  <si>
     <t>Acción dónde un administrador podrá crear una reserva.</t>
   </si>
   <si>
@@ -1958,13 +1934,154 @@
   </si>
   <si>
     <t>Filtro {Residente.identificador}/Listar {Residente.nombre,Residente.apellido,Residente.correo}</t>
+  </si>
+  <si>
+    <t>identificadorTurno</t>
+  </si>
+  <si>
+    <t>numeroTurnoTurno</t>
+  </si>
+  <si>
+    <t>horaInicioTurno</t>
+  </si>
+  <si>
+    <t>horaFinTurno</t>
+  </si>
+  <si>
+    <t>estadoTurno</t>
+  </si>
+  <si>
+    <t>identificadorAgenda</t>
+  </si>
+  <si>
+    <t>nombreAgenda</t>
+  </si>
+  <si>
+    <t>disponibilidadAgenda</t>
+  </si>
+  <si>
+    <t>fechaHoraInicioAgenda</t>
+  </si>
+  <si>
+    <t>fechaHoraFinAgenda</t>
+  </si>
+  <si>
+    <t>Alfanumérico</t>
+  </si>
+  <si>
+    <t>identificadorZonaComun</t>
+  </si>
+  <si>
+    <t>NombreZonaComun</t>
+  </si>
+  <si>
+    <t>capacidadPersonasZonaComun</t>
+  </si>
+  <si>
+    <t>descripcionZonaComun</t>
+  </si>
+  <si>
+    <t>normasZonaComun</t>
+  </si>
+  <si>
+    <t>tiempoUsoZonaComun</t>
+  </si>
+  <si>
+    <t>identificadorUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>nombreUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>abreviaturaUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>enBaseUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>identificadorConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>nombreConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>Quitar espacios en blanco al inicio, al final, y entre palabras.</t>
+  </si>
+  <si>
+    <t>no puede ser negativo</t>
+  </si>
+  <si>
+    <t>No puede ser mayor a 24</t>
+  </si>
+  <si>
+    <t>Sólo letras sin espeacia en medio</t>
+  </si>
+  <si>
+    <t>True/false</t>
+  </si>
+  <si>
+    <t>Formato hora/minutos</t>
+  </si>
+  <si>
+    <t>Activo/inaptivo</t>
+  </si>
+  <si>
+    <t>Disponible/No disponible</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada agenda residencial sea único.</t>
+  </si>
+  <si>
+    <t>Este es un dato tipo texto que representa el nombre de como se llama la agenda que se esta programando</t>
+  </si>
+  <si>
+    <t>Este dato es un tipo logico que representa si esta disponible o no la agenda</t>
+  </si>
+  <si>
+    <t>Este dato representa la fecha de hora de inicio en la cual empieza la agenda.</t>
+  </si>
+  <si>
+    <t>Este dato representa la fecha de hora final en la cual finaliza una agenda.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del normas del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Agendas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2017,13 +2134,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
@@ -2038,7 +2148,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2093,6 +2203,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="45">
     <border>
@@ -2657,7 +2779,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2780,10 +2902,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2862,92 +2981,197 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3029,113 +3253,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3167,17 +3295,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3188,11 +3310,29 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3579,19 +3719,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC31824-1358-4896-8FEC-CA18F2D1F29C}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="72"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3599,7 +3739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,7 +3747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -3615,52 +3755,52 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -3676,7 +3816,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{270AC7B1-5317-4DF0-8E73-05A502D22732}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3686,26 +3826,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DC33F5-6024-4ECE-8864-A6190D431B22}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="8"/>
+    <col min="1" max="1" width="21.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="76"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C1" s="73"/>
+      <c r="D1" s="74"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -3719,44 +3859,44 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="77" t="str">
+        <v>21</v>
+      </c>
+      <c r="D3" s="75" t="str">
         <f>$B$1</f>
         <v>Agendas</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="78"/>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="D4" s="76"/>
+    </row>
+    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="79"/>
+      <c r="D5" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3775,173 +3915,173 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0BC2B36-176F-457B-9E5A-2C1354FBA2A7}">
   <dimension ref="A1:U25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="51.140625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="51.109375" style="8" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="156" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="87" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="157" t="str">
+      <c r="B2" s="88" t="str">
         <f>'Listado Objetos de Dominio'!A3</f>
         <v>Reserva</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="158" t="str">
+        <v>24</v>
+      </c>
+      <c r="B3" s="89" t="str">
         <f>'Listado Objetos de Dominio'!B3</f>
         <v>Corresponde a cada una de las reservas que pude hacer el residente, es decir, el residente puede reservar una zona común, ejemplo: El residente 001 reserva la piscina con su respectivo turno.</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="158"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="158"/>
-      <c r="O3" s="158"/>
-      <c r="P3" s="158"/>
-      <c r="Q3" s="158"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="I4" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="J4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="K4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="L4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="M4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="N4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="O4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="P4" s="17" t="s">
         <v>40</v>
-      </c>
-      <c r="P4" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="65" t="s">
-        <v>131</v>
-      </c>
-      <c r="S4" s="66" t="str">
+      <c r="R4" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="S4" s="65" t="str">
         <f>A22</f>
         <v>Buscar</v>
       </c>
-      <c r="T4" s="67" t="str">
+      <c r="T4" s="66" t="str">
         <f>A23</f>
         <v>Modificar</v>
       </c>
-      <c r="U4" s="68" t="str">
+      <c r="U4" s="67" t="str">
         <f>A25</f>
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>9</v>
@@ -3957,47 +4097,47 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
       <c r="I5" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="21"/>
       <c r="L5" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="R5" s="69" t="s">
-        <v>164</v>
+        <v>86</v>
+      </c>
+      <c r="R5" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -4006,47 +4146,47 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J6" s="19"/>
       <c r="K6" s="21"/>
       <c r="L6" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P6" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="R6" s="69" t="s">
-        <v>164</v>
+        <v>87</v>
+      </c>
+      <c r="R6" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -4058,42 +4198,42 @@
       <c r="J7" s="19"/>
       <c r="K7" s="21"/>
       <c r="L7" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="R7" s="69" t="s">
-        <v>164</v>
+        <v>84</v>
+      </c>
+      <c r="R7" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S7" s="35" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -4105,321 +4245,321 @@
       <c r="J8" s="19"/>
       <c r="K8" s="19"/>
       <c r="L8" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="R8" s="69" t="s">
-        <v>164</v>
+        <v>85</v>
+      </c>
+      <c r="R8" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S8" s="35" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="153" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="154"/>
-      <c r="C10" s="155"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="85"/>
+      <c r="C10" s="86"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="92" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="91"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="106" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="159" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="161" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="160"/>
-      <c r="B13" s="162"/>
-      <c r="C13" s="31" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="141" t="s">
+      <c r="B15" s="107"/>
+      <c r="C15" s="110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="142"/>
-      <c r="C15" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="142"/>
-      <c r="H15" s="138" t="s">
+      <c r="I15" s="105"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="139"/>
-      <c r="J15" s="140"/>
-      <c r="K15" s="138" t="s">
+      <c r="L15" s="105"/>
+      <c r="M15" s="105"/>
+      <c r="N15" s="105"/>
+      <c r="O15" s="79"/>
+      <c r="P15" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="140"/>
-      <c r="P15" s="138" t="s">
+      <c r="Q15" s="79"/>
+      <c r="R15" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="Q15" s="140"/>
-      <c r="R15" s="138" t="s">
+      <c r="S15" s="80"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="108"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="S15" s="149"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="143"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="147"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="47" t="s">
+      <c r="I16" s="32" t="s">
         <v>56</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>57</v>
       </c>
       <c r="J16" s="32" t="s">
         <v>2</v>
       </c>
       <c r="K16" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="M16" s="151"/>
-      <c r="N16" s="151"/>
-      <c r="O16" s="152"/>
+      <c r="M16" s="82"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="83"/>
       <c r="P16" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q16" s="32" t="s">
         <v>2</v>
       </c>
       <c r="R16" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="S16" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="S16" s="33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="130" t="s">
-        <v>131</v>
-      </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="107" t="s">
-        <v>192</v>
-      </c>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="88" t="str">
+    </row>
+    <row r="17" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="98"/>
+      <c r="C17" s="141" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="142"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="122" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I17" s="136" t="str">
+      <c r="I17" s="103" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
-      <c r="J17" s="88" t="str">
+      <c r="J17" s="122" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",$B$2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Reserva</v>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="118"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="151"/>
+      <c r="N17" s="151"/>
+      <c r="O17" s="152"/>
       <c r="P17" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="S17" s="48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="99"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="144"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="154"/>
+      <c r="N18" s="154"/>
+      <c r="O18" s="155"/>
+      <c r="P18" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q18" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="Q17" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S17" s="49" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="132"/>
-      <c r="B18" s="133"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="112"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="56"/>
-      <c r="L18" s="119"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="121"/>
-      <c r="P18" s="14" t="s">
+      <c r="R18" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="S18" s="48" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="154"/>
+      <c r="N19" s="154"/>
+      <c r="O19" s="155"/>
+      <c r="P19" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q19" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="Q18" s="13" t="s">
+      <c r="R19" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="S19" s="48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="154"/>
+      <c r="N20" s="154"/>
+      <c r="O20" s="155"/>
+      <c r="P20" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="S20" s="48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="101"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="148"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="124"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="R21" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="R18" s="13" t="s">
+      <c r="S21" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="S18" s="49" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="132"/>
-      <c r="B19" s="133"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="137"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="56"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="120"/>
-      <c r="N19" s="120"/>
-      <c r="O19" s="121"/>
-      <c r="P19" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q19" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="S19" s="49" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="132"/>
-      <c r="B20" s="133"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="119"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="120"/>
-      <c r="O20" s="121"/>
-      <c r="P20" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q20" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="R20" s="13" t="s">
+    </row>
+    <row r="22" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="156" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="157"/>
+      <c r="C22" s="158" t="s">
         <v>185</v>
       </c>
-      <c r="S20" s="49" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="134"/>
-      <c r="B21" s="135"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="56"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="S21" s="49" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="122" t="s">
-        <v>151</v>
-      </c>
-      <c r="B22" s="123"/>
-      <c r="C22" s="124" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="126"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="159"/>
+      <c r="G22" s="160"/>
       <c r="H22" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I22" s="60" t="str">
+      <c r="I22" s="59" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
@@ -4427,113 +4567,113 @@
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de una  ",$B$2," en un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de una  Reserva en un conjunto residencial.</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="L22" s="94" t="s">
+        <v>193</v>
+      </c>
+      <c r="M22" s="95"/>
+      <c r="N22" s="95"/>
+      <c r="O22" s="96"/>
+      <c r="P22" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="L22" s="127" t="s">
-        <v>201</v>
-      </c>
-      <c r="M22" s="128"/>
-      <c r="N22" s="128"/>
-      <c r="O22" s="129"/>
-      <c r="P22" s="23" t="s">
-        <v>178</v>
-      </c>
       <c r="Q22" s="35" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="R22" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="S22" s="61" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="103" t="s">
-        <v>156</v>
-      </c>
-      <c r="B23" s="104"/>
-      <c r="C23" s="91" t="s">
-        <v>194</v>
-      </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="99" t="str">
+        <v>128</v>
+      </c>
+      <c r="S22" s="60" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="137" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="138"/>
+      <c r="C23" s="125" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="133" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I23" s="101" t="str">
+      <c r="I23" s="135" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
-      <c r="J23" s="99" t="str">
+      <c r="J23" s="133" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar de la ",$B$2)</f>
         <v>Corresponde a los datos que se van a modificar de la Reserva</v>
       </c>
-      <c r="K23" s="97"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="93"/>
-      <c r="P23" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q23" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="R23" s="63" t="s">
-        <v>188</v>
-      </c>
-      <c r="S23" s="64" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="105"/>
-      <c r="B24" s="106"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="95"/>
-      <c r="N24" s="95"/>
-      <c r="O24" s="96"/>
-      <c r="P24" s="62" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q24" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="R24" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="S24" s="70" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82" t="s">
-        <v>195</v>
-      </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="84"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="126"/>
+      <c r="N23" s="126"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q23" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="R23" s="62" t="s">
+        <v>181</v>
+      </c>
+      <c r="S23" s="63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="139"/>
+      <c r="B24" s="140"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="129"/>
+      <c r="N24" s="129"/>
+      <c r="O24" s="130"/>
+      <c r="P24" s="61" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q24" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="R24" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="S24" s="69" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="114" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" s="115"/>
+      <c r="C25" s="116" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="118"/>
       <c r="H25" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I25" s="25" t="s">
         <v>9</v>
@@ -4543,41 +4683,25 @@
         <v>Corresponde al identificador de la Reserva  que se quiere dar de baja.</v>
       </c>
       <c r="K25" s="40"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="87"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="120"/>
+      <c r="N25" s="120"/>
+      <c r="O25" s="121"/>
       <c r="P25" s="25" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Q25" s="41" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R25" s="41" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S25" s="41" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="A17:B21"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:G16"/>
-    <mergeCell ref="H15:J15"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="L25:O25"/>
@@ -4594,8 +4718,24 @@
     <mergeCell ref="L17:O20"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:G22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="A17:B21"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="K15:O15"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:G16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{5CF40659-DFE6-490B-8F27-C76F1B381885}"/>
     <hyperlink ref="A1:Q1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{10212072-64F9-4E47-AEF7-64DC2E58CFB9}"/>
@@ -4623,173 +4763,173 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037CC029-DC44-4605-90F4-CA51C57B9385}">
   <dimension ref="A1:U32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="156" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="87" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="157" t="str">
+      <c r="B2" s="88" t="str">
         <f>'Listado Objetos de Dominio'!A5</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="158" t="str">
+        <v>24</v>
+      </c>
+      <c r="B3" s="89" t="str">
         <f>'Listado Objetos de Dominio'!B5</f>
         <v>Corresponde a la persona que puede realizar una reserva para una zona común.</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="158"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="158"/>
-      <c r="O3" s="158"/>
-      <c r="P3" s="158"/>
-      <c r="Q3" s="158"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="I4" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="J4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="K4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="L4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="M4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="N4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="O4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="P4" s="17" t="s">
         <v>40</v>
-      </c>
-      <c r="P4" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="65" t="s">
-        <v>131</v>
-      </c>
-      <c r="S4" s="66" t="str">
+      <c r="R4" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="S4" s="65" t="str">
         <f>A30</f>
         <v>Buscar</v>
       </c>
-      <c r="T4" s="67" t="str">
+      <c r="T4" s="66" t="str">
         <f>A31</f>
         <v>Modificar</v>
       </c>
-      <c r="U4" s="68" t="str">
+      <c r="U4" s="67" t="str">
         <f>A32</f>
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>9</v>
@@ -4805,44 +4945,44 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
       <c r="I5" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="21"/>
       <c r="L5" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M5" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="R5" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S5" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="T5" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="U5" s="25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
         <v>45</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="R5" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="S5" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="T5" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="U5" s="25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>46</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>8</v>
@@ -4858,46 +4998,46 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J6" s="19"/>
       <c r="K6" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P6" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="R6" s="69" t="s">
-        <v>164</v>
+        <v>93</v>
+      </c>
+      <c r="R6" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>8</v>
@@ -4913,46 +5053,46 @@
       <c r="G7" s="19"/>
       <c r="H7" s="19"/>
       <c r="I7" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="R7" s="69" t="s">
-        <v>164</v>
+        <v>95</v>
+      </c>
+      <c r="R7" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>8</v>
@@ -4968,46 +5108,46 @@
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="19"/>
       <c r="K8" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="R8" s="69" t="s">
-        <v>164</v>
+        <v>97</v>
+      </c>
+      <c r="R8" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>13</v>
@@ -5019,44 +5159,44 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
       <c r="L9" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="R9" s="69" t="s">
-        <v>164</v>
+        <v>100</v>
+      </c>
+      <c r="R9" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U9" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>11</v>
@@ -5068,44 +5208,44 @@
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
       <c r="I10" s="20" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="21"/>
       <c r="L10" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P10" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="R10" s="69" t="s">
-        <v>164</v>
+        <v>103</v>
+      </c>
+      <c r="R10" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U10" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>13</v>
@@ -5117,46 +5257,46 @@
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M11" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O11" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="R11" s="69" t="s">
-        <v>164</v>
+        <v>105</v>
+      </c>
+      <c r="R11" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U11" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>9</v>
@@ -5172,46 +5312,46 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
       <c r="I12" s="20" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N12" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O12" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="R12" s="69" t="s">
-        <v>164</v>
+        <v>108</v>
+      </c>
+      <c r="R12" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U12" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="67.5" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="69" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>9</v>
@@ -5227,49 +5367,49 @@
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="20" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J13" s="19"/>
       <c r="K13" s="21" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P13" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="R13" s="69" t="s">
-        <v>164</v>
+        <v>112</v>
+      </c>
+      <c r="R13" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U13" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -5278,402 +5418,402 @@
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="20" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J14" s="19"/>
       <c r="K14" s="21"/>
       <c r="L14" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M14" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O14" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P14" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="R14" s="69" t="s">
-        <v>164</v>
+        <v>116</v>
+      </c>
+      <c r="R14" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S14" s="35" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U14" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="176" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="176"/>
-      <c r="C16" s="176"/>
-      <c r="E16" s="176" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="176"/>
-      <c r="G16" s="176"/>
-      <c r="I16" s="176" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="161" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="161"/>
+      <c r="C16" s="161"/>
+      <c r="E16" s="161" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="161"/>
+      <c r="G16" s="161"/>
+      <c r="I16" s="161" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="161"/>
+      <c r="K16" s="161"/>
+    </row>
+    <row r="17" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
         <v>48</v>
-      </c>
-      <c r="J16" s="176"/>
-      <c r="K16" s="176"/>
-    </row>
-    <row r="17" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
-        <v>49</v>
       </c>
       <c r="B17" s="28" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" s="28" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J17" s="28" t="s">
         <v>2</v>
       </c>
       <c r="K17" s="28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="162" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="163" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="164" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="163" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="163" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="164" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="162" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" s="163" t="s">
+        <v>123</v>
+      </c>
+      <c r="K18" s="164" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="162"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="164"/>
+      <c r="E19" s="163"/>
+      <c r="F19" s="163"/>
+      <c r="G19" s="164"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="164"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="162"/>
+      <c r="B20" s="163"/>
+      <c r="C20" s="164" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="163"/>
+      <c r="F20" s="163"/>
+      <c r="G20" s="164"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="163"/>
+      <c r="K20" s="164"/>
+    </row>
+    <row r="21" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="162"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="164"/>
+      <c r="E21" s="163"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="164"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="164"/>
+    </row>
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="106" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="174" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="175" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18" s="173" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="175" t="s">
-        <v>127</v>
-      </c>
-      <c r="F18" s="175" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" s="173" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="45"/>
-      <c r="I18" s="174" t="s">
-        <v>129</v>
-      </c>
-      <c r="J18" s="175" t="s">
-        <v>130</v>
-      </c>
-      <c r="K18" s="173" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="174"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="173"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="175"/>
-      <c r="G19" s="173"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="173"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="174"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="173" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="173"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="173"/>
-    </row>
-    <row r="21" spans="1:19" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="174"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="173"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="175"/>
-      <c r="G21" s="173"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="173"/>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="141" t="s">
+      <c r="B23" s="107"/>
+      <c r="C23" s="110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="142"/>
-      <c r="C23" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="142"/>
-      <c r="H23" s="138" t="s">
+      <c r="I23" s="105"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="139"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="138" t="s">
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="139"/>
-      <c r="M23" s="139"/>
-      <c r="N23" s="139"/>
-      <c r="O23" s="140"/>
-      <c r="P23" s="138" t="s">
+      <c r="Q23" s="79"/>
+      <c r="R23" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="140"/>
-      <c r="R23" s="138" t="s">
+      <c r="S23" s="80"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="108"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="113"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="113"/>
+      <c r="G24" s="109"/>
+      <c r="H24" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="S23" s="149"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="143"/>
-      <c r="B24" s="144"/>
-      <c r="C24" s="147"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="47" t="s">
+      <c r="I24" s="32" t="s">
         <v>56</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>57</v>
       </c>
       <c r="J24" s="32" t="s">
         <v>2</v>
       </c>
       <c r="K24" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="151"/>
-      <c r="N24" s="151"/>
-      <c r="O24" s="152"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="83"/>
       <c r="P24" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q24" s="32" t="s">
         <v>2</v>
       </c>
       <c r="R24" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="S24" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="S24" s="33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="130" t="s">
-        <v>131</v>
-      </c>
-      <c r="B25" s="131"/>
-      <c r="C25" s="107" t="s">
-        <v>132</v>
-      </c>
-      <c r="D25" s="108"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="88" t="str">
+    </row>
+    <row r="25" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="98"/>
+      <c r="C25" s="141" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="142"/>
+      <c r="E25" s="142"/>
+      <c r="F25" s="142"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="122" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I25" s="136" t="str">
+      <c r="I25" s="103" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J25" s="171" t="str">
+      <c r="J25" s="173" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Residente</v>
       </c>
-      <c r="K25" s="48"/>
-      <c r="L25" s="116"/>
-      <c r="M25" s="117"/>
-      <c r="N25" s="117"/>
-      <c r="O25" s="118"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="150"/>
+      <c r="M25" s="151"/>
+      <c r="N25" s="151"/>
+      <c r="O25" s="152"/>
       <c r="P25" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q25" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="R25" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="S25" s="48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="99"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="145"/>
+      <c r="G26" s="146"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="174"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="153"/>
+      <c r="M26" s="154"/>
+      <c r="N26" s="154"/>
+      <c r="O26" s="155"/>
+      <c r="P26" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q26" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="S26" s="48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="99"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="146"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="153"/>
+      <c r="M27" s="154"/>
+      <c r="N27" s="154"/>
+      <c r="O27" s="155"/>
+      <c r="P27" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="Q25" s="13" t="s">
+      <c r="Q27" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="R25" s="13" t="s">
+      <c r="R27" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="S25" s="49" t="s">
+      <c r="S27" s="48" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="132"/>
-      <c r="B26" s="133"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="172"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="120"/>
-      <c r="N26" s="120"/>
-      <c r="O26" s="121"/>
-      <c r="P26" s="14" t="s">
+    <row r="28" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="99"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="145"/>
+      <c r="G28" s="146"/>
+      <c r="H28" s="123"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="154"/>
+      <c r="O28" s="155"/>
+      <c r="P28" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="Q26" s="13" t="s">
+      <c r="Q28" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="R26" s="13" t="s">
+      <c r="R28" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="S26" s="49" t="s">
+      <c r="S28" s="48" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="101"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q29" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="R29" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="S29" s="48" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="132"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="137"/>
-      <c r="J27" s="172"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="120"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q27" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="R27" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="S27" s="49" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="132"/>
-      <c r="B28" s="133"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="112"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="172"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="120"/>
-      <c r="N28" s="120"/>
-      <c r="O28" s="121"/>
-      <c r="P28" s="14" t="s">
+    <row r="30" spans="1:19" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="156" t="s">
         <v>144</v>
       </c>
-      <c r="Q28" s="13" t="s">
+      <c r="B30" s="157"/>
+      <c r="C30" s="158" t="s">
         <v>145</v>
       </c>
-      <c r="R28" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="S28" s="49" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="134"/>
-      <c r="B29" s="135"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="55"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="59"/>
-      <c r="P29" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q29" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="R29" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="S29" s="49" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="122" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="123"/>
-      <c r="C30" s="124" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="125"/>
-      <c r="E30" s="125"/>
-      <c r="F30" s="125"/>
-      <c r="G30" s="126"/>
+      <c r="D30" s="159"/>
+      <c r="E30" s="159"/>
+      <c r="F30" s="159"/>
+      <c r="G30" s="160"/>
       <c r="H30" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I30" s="60" t="str">
+      <c r="I30" s="59" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
@@ -5681,40 +5821,40 @@
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de un  ",B2," de un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de un  Residente de un conjunto residencial.</v>
       </c>
-      <c r="K30" s="46" t="s">
-        <v>153</v>
-      </c>
-      <c r="L30" s="127" t="s">
-        <v>172</v>
-      </c>
-      <c r="M30" s="128"/>
-      <c r="N30" s="128"/>
-      <c r="O30" s="129"/>
+      <c r="K30" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="L30" s="94" t="s">
+        <v>165</v>
+      </c>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="96"/>
       <c r="P30" s="23" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="Q30" s="35" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="R30" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="S30" s="61" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="163" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="164"/>
-      <c r="C31" s="165" t="s">
-        <v>157</v>
-      </c>
-      <c r="D31" s="166"/>
-      <c r="E31" s="166"/>
-      <c r="F31" s="166"/>
-      <c r="G31" s="167"/>
+        <v>128</v>
+      </c>
+      <c r="S30" s="60" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="165" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" s="166"/>
+      <c r="C31" s="167" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="168"/>
+      <c r="E31" s="168"/>
+      <c r="F31" s="168"/>
+      <c r="G31" s="169"/>
       <c r="H31" s="36" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
@@ -5728,37 +5868,37 @@
         <v>Corresponde a los datos que se van a modificar del Residente</v>
       </c>
       <c r="K31" s="38"/>
-      <c r="L31" s="168"/>
-      <c r="M31" s="169"/>
-      <c r="N31" s="169"/>
-      <c r="O31" s="170"/>
-      <c r="P31" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q31" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="R31" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="S31" s="64" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" s="81"/>
-      <c r="C32" s="82" t="s">
-        <v>163</v>
-      </c>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="84"/>
+      <c r="L31" s="170"/>
+      <c r="M31" s="171"/>
+      <c r="N31" s="171"/>
+      <c r="O31" s="172"/>
+      <c r="P31" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q31" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="R31" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="S31" s="63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="114" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="115"/>
+      <c r="C32" s="116" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="118"/>
       <c r="H32" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I32" s="25" t="s">
         <v>9</v>
@@ -5768,48 +5908,25 @@
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
       <c r="K32" s="40"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="86"/>
-      <c r="N32" s="86"/>
-      <c r="O32" s="87"/>
+      <c r="L32" s="119"/>
+      <c r="M32" s="120"/>
+      <c r="N32" s="120"/>
+      <c r="O32" s="121"/>
       <c r="P32" s="25" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="Q32" s="41" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R32" s="41" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="S32" s="41" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="J18:J21"/>
-    <mergeCell ref="K18:K21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:G24"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:O23"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="C32:G32"/>
     <mergeCell ref="L32:O32"/>
@@ -5825,6 +5942,29 @@
     <mergeCell ref="I25:I28"/>
     <mergeCell ref="J25:J28"/>
     <mergeCell ref="L25:O28"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:G24"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:O23"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="I16:K16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{1AE4FE85-AF13-4BAA-9ECE-73FAE508027B}"/>
@@ -5855,174 +5995,174 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC57795F-B02D-497B-A04E-44BC1D3D4128}">
-  <dimension ref="A1:U25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30" style="180" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="156" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="87" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="157" t="str">
+      <c r="B2" s="88" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Turno</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="158" t="str">
+        <v>24</v>
+      </c>
+      <c r="B3" s="89" t="str">
         <f>'Listado Objetos de Dominio'!B4</f>
         <v>Corresponde a los turnos que un residente puede reservar en una agenda, es decir, el residente toma un turno que esta disponible de una agenda que anteriormente ya esta programada.</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="158"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="158"/>
-      <c r="O3" s="158"/>
-      <c r="P3" s="158"/>
-      <c r="Q3" s="158"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="I4" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="J4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="K4" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="L4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="M4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="N4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="O4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="P4" s="17" t="s">
         <v>40</v>
-      </c>
-      <c r="P4" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="65" t="s">
-        <v>131</v>
-      </c>
-      <c r="S4" s="66" t="str">
-        <f>A23</f>
+      <c r="R4" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="S4" s="65" t="str">
+        <f>A39</f>
         <v>Buscar</v>
       </c>
-      <c r="T4" s="67" t="str">
-        <f>A24</f>
+      <c r="T4" s="66" t="str">
+        <f>A40</f>
         <v>Modificar</v>
       </c>
-      <c r="U4" s="68" t="str">
-        <f>A25</f>
+      <c r="U4" s="67" t="str">
+        <f>A41</f>
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>9</v>
@@ -6038,44 +6178,44 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
       <c r="I5" s="20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="21"/>
       <c r="L5" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="R5" s="69" t="s">
-        <v>164</v>
+        <v>71</v>
+      </c>
+      <c r="R5" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
-        <v>75</v>
+        <v>203</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>8</v>
@@ -6091,49 +6231,47 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J6" s="19"/>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="21"/>
+      <c r="L6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R6" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S6" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="T6" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="U6" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="O6" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="R6" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="S6" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="T6" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="U6" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>62</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -6142,47 +6280,45 @@
       <c r="G7" s="19"/>
       <c r="H7" s="19"/>
       <c r="I7" s="20" t="s">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
+      <c r="K7" s="21" t="s">
+        <v>226</v>
+      </c>
       <c r="L7" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="R7" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="S7" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="T7" s="24" t="s">
-        <v>168</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="R7" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S7" s="23"/>
+      <c r="T7" s="24"/>
       <c r="U7" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -6191,47 +6327,45 @@
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="20" t="s">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="J8" s="19"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="19" t="s">
-        <v>45</v>
+      <c r="K8" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>44</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="R8" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="S8" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="T8" s="24" t="s">
-        <v>168</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="R8" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S8" s="23"/>
+      <c r="T8" s="24"/>
       <c r="U8" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -6240,460 +6374,1269 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="20" t="s">
-        <v>65</v>
+        <v>231</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="21"/>
       <c r="L9" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="R9" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="T9" s="24" t="s">
-        <v>168</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="R9" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S9" s="23"/>
+      <c r="T9" s="24"/>
       <c r="U9" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
-        <v>71</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
+        <v>207</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+        <v>9</v>
+      </c>
+      <c r="C10" s="19">
+        <v>32</v>
+      </c>
+      <c r="D10" s="19">
+        <v>32</v>
+      </c>
       <c r="E10" s="19"/>
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
-      <c r="I10" s="20"/>
+      <c r="I10" s="20" t="s">
+        <v>64</v>
+      </c>
       <c r="J10" s="19"/>
-      <c r="K10" s="21"/>
+      <c r="K10" s="20"/>
       <c r="L10" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O10" s="19" t="s">
         <v>44</v>
       </c>
       <c r="P10" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="R10" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="S10" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="T10" s="24" t="s">
-        <v>166</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="R10" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S10" s="35"/>
+      <c r="T10" s="24"/>
       <c r="U10" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="153" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="19">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19">
+        <v>50</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="R11" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S11" s="35"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="R12" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S12" s="35"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="J13" s="19"/>
+      <c r="K13" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="R13" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S13" s="35"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="J14" s="19"/>
+      <c r="K14" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="R14" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S14" s="35"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" s="185" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="19">
+        <v>32</v>
+      </c>
+      <c r="D15" s="19">
+        <v>32</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q15" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="R15" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S15" s="186" t="s">
+        <v>160</v>
+      </c>
+      <c r="T15" s="187" t="s">
+        <v>161</v>
+      </c>
+      <c r="U15" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="19">
+        <v>3</v>
+      </c>
+      <c r="D16" s="19">
+        <v>50</v>
+      </c>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="19"/>
+      <c r="K16" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="R16" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S16" s="35"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19">
+        <v>4</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="19"/>
+      <c r="K17" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="R17" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S17" s="35"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19">
+        <v>255</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="19"/>
+      <c r="K18" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="R18" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S18" s="35"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19">
+        <v>5000</v>
+      </c>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J19" s="19"/>
+      <c r="K19" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="R19" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S19" s="35"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="19">
+        <v>1</v>
+      </c>
+      <c r="D20" s="19">
+        <v>5</v>
+      </c>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19">
+        <v>3600</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="R20" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S20" s="35"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" s="19">
+        <v>32</v>
+      </c>
+      <c r="D21" s="19">
+        <v>32</v>
+      </c>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O21" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="R21" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S21" s="35" t="str">
+        <f>_xlfn.CONCAT(L21,$B$5)</f>
+        <v>SiAlfanumerico</v>
+      </c>
+      <c r="T21" s="24" t="str">
+        <f>_xlfn.CONCAT(M21,$B$5)</f>
+        <v>NoAlfanumerico</v>
+      </c>
+      <c r="U21" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="19">
+        <v>3</v>
+      </c>
+      <c r="D22" s="19">
+        <v>50</v>
+      </c>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="19"/>
+      <c r="K22" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O22" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="R22" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S22" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="T22" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="U22" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="19">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19">
+        <v>3</v>
+      </c>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="J23" s="19"/>
+      <c r="K23" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P23" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q23" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="R23" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S23" s="35"/>
+      <c r="T23" s="24"/>
+      <c r="U23" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="19">
+        <v>4</v>
+      </c>
+      <c r="D24" s="19">
+        <v>5</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="J24" s="19"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N24" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O24" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P24" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q24" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="R24" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S24" s="35"/>
+      <c r="T24" s="24"/>
+      <c r="U24" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" s="19">
+        <v>32</v>
+      </c>
+      <c r="D25" s="19">
+        <v>32</v>
+      </c>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="19"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N25" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O25" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P25" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q25" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="R25" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S25" s="35"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="19">
+        <v>1</v>
+      </c>
+      <c r="D26" s="19">
+        <v>50</v>
+      </c>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="19"/>
+      <c r="K26" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N26" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P26" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q26" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="R26" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="S26" s="35"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="84" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="85"/>
+      <c r="C28" s="86"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="154"/>
-      <c r="C12" s="155"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="B29" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="28" t="s">
+    </row>
+    <row r="30" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="175"/>
+      <c r="B31" s="176"/>
+      <c r="C31" s="30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="175"/>
+      <c r="B32" s="176"/>
+      <c r="C32" s="30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="91"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="106" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="107"/>
+      <c r="C35" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="29" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="159" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" s="161" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="180"/>
-      <c r="B15" s="181"/>
-      <c r="C15" s="30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="180"/>
-      <c r="B16" s="181"/>
-      <c r="C16" s="30" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="160"/>
-      <c r="B17" s="162"/>
-      <c r="C17" s="42" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="141" t="s">
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="107"/>
+      <c r="H35" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="142"/>
-      <c r="C19" s="145" t="s">
+      <c r="I35" s="105"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="78" t="s">
+        <v>52</v>
+      </c>
+      <c r="L35" s="105"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105"/>
+      <c r="O35" s="79"/>
+      <c r="P35" s="78" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q35" s="79"/>
+      <c r="R35" s="78" t="s">
+        <v>54</v>
+      </c>
+      <c r="S35" s="80"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="108"/>
+      <c r="B36" s="109"/>
+      <c r="C36" s="112"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="109"/>
+      <c r="H36" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="I36" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="146"/>
-      <c r="E19" s="146"/>
-      <c r="F19" s="146"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="138" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" s="139"/>
-      <c r="J19" s="140"/>
-      <c r="K19" s="138" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" s="139"/>
-      <c r="M19" s="139"/>
-      <c r="N19" s="139"/>
-      <c r="O19" s="140"/>
-      <c r="P19" s="138" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q19" s="140"/>
-      <c r="R19" s="138" t="s">
-        <v>55</v>
-      </c>
-      <c r="S19" s="149"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="143"/>
-      <c r="B20" s="144"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="148"/>
-      <c r="E20" s="148"/>
-      <c r="F20" s="148"/>
-      <c r="G20" s="144"/>
-      <c r="H20" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="32" t="s">
+      <c r="K36" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36" s="81" t="s">
+        <v>2</v>
+      </c>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="83"/>
+      <c r="P36" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="32" t="s">
+      <c r="Q36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="K20" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="150" t="s">
-        <v>2</v>
-      </c>
-      <c r="M20" s="151"/>
-      <c r="N20" s="151"/>
-      <c r="O20" s="152"/>
-      <c r="P20" s="32" t="s">
+      <c r="R36" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="Q20" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="R20" s="32" t="s">
+      <c r="S36" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="S20" s="33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="130" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" s="131"/>
-      <c r="C21" s="107" t="s">
-        <v>196</v>
-      </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="88" t="str">
+    </row>
+    <row r="37" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="98"/>
+      <c r="C37" s="141" t="s">
+        <v>188</v>
+      </c>
+      <c r="D37" s="142"/>
+      <c r="E37" s="142"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="143"/>
+      <c r="H37" s="122" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
       </c>
-      <c r="I21" s="88" t="str">
+      <c r="I37" s="122" t="str">
         <f>B2</f>
         <v>Turno</v>
       </c>
-      <c r="J21" s="88" t="str">
+      <c r="J37" s="122" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",$B$2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Turno</v>
       </c>
-      <c r="K21" s="48"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="117"/>
-      <c r="N21" s="117"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S21" s="49" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="132"/>
-      <c r="B22" s="133"/>
-      <c r="C22" s="110"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="112"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="119"/>
-      <c r="M22" s="120"/>
-      <c r="N22" s="120"/>
-      <c r="O22" s="121"/>
-      <c r="P22" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="S22" s="49" t="s">
+      <c r="K37" s="181"/>
+      <c r="L37" s="150"/>
+      <c r="M37" s="151"/>
+      <c r="N37" s="151"/>
+      <c r="O37" s="152"/>
+      <c r="P37" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q37" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="R37" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="S37" s="48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="99"/>
+      <c r="B38" s="100"/>
+      <c r="C38" s="144"/>
+      <c r="D38" s="145"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="145"/>
+      <c r="G38" s="146"/>
+      <c r="H38" s="123"/>
+      <c r="I38" s="123"/>
+      <c r="J38" s="123"/>
+      <c r="K38" s="182"/>
+      <c r="L38" s="153"/>
+      <c r="M38" s="154"/>
+      <c r="N38" s="154"/>
+      <c r="O38" s="155"/>
+      <c r="P38" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q38" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="R38" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="S38" s="48" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="156" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="157"/>
+      <c r="C39" s="158" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="122" t="s">
-        <v>151</v>
-      </c>
-      <c r="B23" s="123"/>
-      <c r="C23" s="124" t="s">
-        <v>197</v>
-      </c>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="34" t="str">
+      <c r="D39" s="159"/>
+      <c r="E39" s="159"/>
+      <c r="F39" s="159"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
       </c>
-      <c r="I23" s="34" t="str">
+      <c r="I39" s="34" t="str">
         <f>B2</f>
         <v>Turno</v>
       </c>
-      <c r="J23" s="34" t="str">
+      <c r="J39" s="34" t="str">
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de un  ",$B$2," en un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de un  Turno en un conjunto residencial.</v>
       </c>
-      <c r="K23" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="L23" s="127" t="s">
-        <v>202</v>
-      </c>
-      <c r="M23" s="128"/>
-      <c r="N23" s="128"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q23" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="R23" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="S23" s="61" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="103" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" s="104"/>
-      <c r="C24" s="177" t="s">
-        <v>198</v>
-      </c>
-      <c r="D24" s="178"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="178"/>
-      <c r="G24" s="179"/>
-      <c r="H24" s="72" t="str">
+      <c r="K39" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="L39" s="94" t="s">
+        <v>194</v>
+      </c>
+      <c r="M39" s="95"/>
+      <c r="N39" s="95"/>
+      <c r="O39" s="96"/>
+      <c r="P39" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q39" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="R39" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="S39" s="60" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="137" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="138"/>
+      <c r="C40" s="177" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" s="178"/>
+      <c r="E40" s="178"/>
+      <c r="F40" s="178"/>
+      <c r="G40" s="179"/>
+      <c r="H40" s="70" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
       </c>
-      <c r="I24" s="72" t="str">
+      <c r="I40" s="70" t="str">
         <f>B2</f>
         <v>Turno</v>
       </c>
-      <c r="J24" s="72" t="str">
+      <c r="J40" s="70" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar del ",$B$2)</f>
         <v>Corresponde a los datos que se van a modificar del Turno</v>
       </c>
-      <c r="K24" s="71"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="92"/>
-      <c r="O24" s="93"/>
-      <c r="P24" s="62" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q24" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="R24" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="S24" s="64" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82" t="s">
-        <v>199</v>
-      </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25" s="25" t="s">
+      <c r="K40" s="183"/>
+      <c r="L40" s="125"/>
+      <c r="M40" s="126"/>
+      <c r="N40" s="126"/>
+      <c r="O40" s="127"/>
+      <c r="P40" s="61" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q40" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="R40" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="S40" s="63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="114" t="s">
+        <v>155</v>
+      </c>
+      <c r="B41" s="115"/>
+      <c r="C41" s="116" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" s="117"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="117"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="J25" s="39" t="str">
+      <c r="J41" s="39" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Turno  que se quiere dar de baja.</v>
       </c>
-      <c r="K25" s="40"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="87"/>
-      <c r="P25" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q25" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="R25" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="S25" s="41" t="s">
-        <v>161</v>
+      <c r="K41" s="184"/>
+      <c r="L41" s="119"/>
+      <c r="M41" s="120"/>
+      <c r="N41" s="120"/>
+      <c r="O41" s="121"/>
+      <c r="P41" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q41" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="R41" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="S41" s="41" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="L41:O41"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="C37:G38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="L40:O40"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="L37:O38"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="L36:O36"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:G20"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="K19:O19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="L21:O22"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:G36"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="P35:Q35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{94AC8755-4E69-45C0-81AE-103982376658}"/>
     <hyperlink ref="A1:Q1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{A07B997A-10B9-47BA-93CF-F21578FD4814}"/>
     <hyperlink ref="A5" location="Residente!A12" display="identificador" xr:uid="{FE597574-E242-4CFD-84B5-8F3665A918D8}"/>
-    <hyperlink ref="C14" location="Turno!A6" display="nombreNumeroTurno" xr:uid="{CF645687-9AC3-474C-86D4-1B0038933112}"/>
-    <hyperlink ref="C17" location="Turno!A10" display="agenda " xr:uid="{DEC19558-A936-43DE-8EA6-CF097F49F857}"/>
-    <hyperlink ref="C15" location="Turno!A7" display="horaInicio" xr:uid="{B80256C5-DB80-4B91-8790-EE8AE23F9C62}"/>
-    <hyperlink ref="C16" location="Turno!A8" display="horaFin" xr:uid="{E22FFD98-CB13-45E8-AE86-B88017669FB9}"/>
-    <hyperlink ref="A10" location="Agenda!A1" display="agenda" xr:uid="{339F36D6-9139-418E-B004-B91A32C78651}"/>
-    <hyperlink ref="A23:B23" location="Turno!S4" display="Buscar" xr:uid="{68F8C658-6991-4982-AA6A-1DF175A78458}"/>
-    <hyperlink ref="A25:B25" location="Turno!U4" display="Eliminar" xr:uid="{797B4F6B-A586-4BB0-8AF6-79C8EA9CBE25}"/>
-    <hyperlink ref="A21:B22" location="Turno!R4" display="Registrar" xr:uid="{4AF6602E-E0E3-4735-97E3-C1225FBF4E72}"/>
-    <hyperlink ref="I25" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{765A0323-7B90-4DEF-ADFF-9DC283307666}"/>
+    <hyperlink ref="C30" location="Turno!A6" display="nombreNumeroTurno" xr:uid="{CF645687-9AC3-474C-86D4-1B0038933112}"/>
+    <hyperlink ref="C33" location="Turno!A10" display="agenda " xr:uid="{DEC19558-A936-43DE-8EA6-CF097F49F857}"/>
+    <hyperlink ref="C31" location="Turno!A7" display="horaInicio" xr:uid="{B80256C5-DB80-4B91-8790-EE8AE23F9C62}"/>
+    <hyperlink ref="C32" location="Turno!A8" display="horaFin" xr:uid="{E22FFD98-CB13-45E8-AE86-B88017669FB9}"/>
+    <hyperlink ref="A39:B39" location="Turno!S4" display="Buscar" xr:uid="{68F8C658-6991-4982-AA6A-1DF175A78458}"/>
+    <hyperlink ref="A41:B41" location="Turno!U4" display="Eliminar" xr:uid="{797B4F6B-A586-4BB0-8AF6-79C8EA9CBE25}"/>
+    <hyperlink ref="A37:B38" location="Turno!R4" display="Registrar" xr:uid="{4AF6602E-E0E3-4735-97E3-C1225FBF4E72}"/>
+    <hyperlink ref="I41" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{765A0323-7B90-4DEF-ADFF-9DC283307666}"/>
     <hyperlink ref="T4" location="Turno!A24" display="Turno!A24" xr:uid="{70F650AA-B42D-4B2B-85F0-CD857D832440}"/>
     <hyperlink ref="U4" location="Turno!A25" display="Turno!A25" xr:uid="{5FDCB866-4F36-45DA-816D-5DB30279642B}"/>
     <hyperlink ref="R4" location="Turno!A21" display="Registrar" xr:uid="{64714A7B-E0B7-4EED-BCE3-5791209D17BE}"/>
     <hyperlink ref="S4" location="Turno!A23" display="Turno!A23" xr:uid="{0318B592-2B3B-4420-8401-7AAE05D11F42}"/>
-    <hyperlink ref="A24:B24" location="Turno!T4" display="Modificar" xr:uid="{1F4FC9B8-A6C4-40AF-8529-21FE0E59FB29}"/>
+    <hyperlink ref="A40:B40" location="Turno!T4" display="Modificar" xr:uid="{1F4FC9B8-A6C4-40AF-8529-21FE0E59FB29}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Reservas.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Reservas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6481F5-058C-441A-970B-7770EB768B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AC1D78-FA01-4D4A-920C-F6611F31C884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{9E75F319-B909-453D-9AFC-FA9C5B40B20E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{9E75F319-B909-453D-9AFC-FA9C5B40B20E}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" r:id="rId1"/>
@@ -1328,7 +1328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="268">
   <si>
     <t>Tipo Objeto Dominio</t>
   </si>
@@ -1465,9 +1465,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>nombre</t>
-  </si>
-  <si>
     <t>Sólo letras y espacios</t>
   </si>
   <si>
@@ -1612,9 +1609,6 @@
     <t>Es un dato que representa el nombre del residente.</t>
   </si>
   <si>
-    <t>apellido</t>
-  </si>
-  <si>
     <t>Es un dato que representa el apellido de un residente</t>
   </si>
   <si>
@@ -1633,9 +1627,6 @@
     <t>Es un dato que representa el numero único del documento de un residente.</t>
   </si>
   <si>
-    <t>fechaNacimiento</t>
-  </si>
-  <si>
     <t>(MM/dd/aaaa)</t>
   </si>
   <si>
@@ -1657,9 +1648,6 @@
     <t>Este dato representa el correo electrónico de un residente</t>
   </si>
   <si>
-    <t>contraseña</t>
-  </si>
-  <si>
     <t>Sólo letras que pueden ser mayúsculas o minusculas, números y los caracteres especiales.</t>
   </si>
   <si>
@@ -1669,18 +1657,6 @@
     <t>este dato representa la contraseña con la que ingresa el residente</t>
   </si>
   <si>
-    <t>inmueble</t>
-  </si>
-  <si>
-    <t>Inmueble</t>
-  </si>
-  <si>
-    <t>zona de Inmueble- tipo de inueble - numero del inmueble</t>
-  </si>
-  <si>
-    <t>Representa el lugar donde vive el residente dentro del conjunto residencial.</t>
-  </si>
-  <si>
     <t>Combinación única 2</t>
   </si>
   <si>
@@ -2075,6 +2051,87 @@
   </si>
   <si>
     <t>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Agendas.</t>
+  </si>
+  <si>
+    <t>identificadorResidente</t>
+  </si>
+  <si>
+    <t>nombreResidente</t>
+  </si>
+  <si>
+    <t>apellidoResidente</t>
+  </si>
+  <si>
+    <t>tipoDocumentoResidente</t>
+  </si>
+  <si>
+    <t>numeroDocumentoResidente</t>
+  </si>
+  <si>
+    <t>fechaNacimientoResidente</t>
+  </si>
+  <si>
+    <t>numeroContactoResidente</t>
+  </si>
+  <si>
+    <t>correoElectronicoResidente</t>
+  </si>
+  <si>
+    <t>contraseñaResidente</t>
+  </si>
+  <si>
+    <t>identificadorInmueble</t>
+  </si>
+  <si>
+    <t>numeroViviendaInmueble</t>
+  </si>
+  <si>
+    <t>identificadorTipoInmueble</t>
+  </si>
+  <si>
+    <t>nombreTipoInmueble</t>
+  </si>
+  <si>
+    <t>identificadorZonaInmueble</t>
+  </si>
+  <si>
+    <t>numeroZonaInmuebleZonaInmueble</t>
+  </si>
+  <si>
+    <t>identificadorTipoZonaInmueble</t>
+  </si>
+  <si>
+    <t>nombreTipoZonaInmueble</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del numeroZonaInmueble del objeto dominio   en el contexto de Contexto.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio TipoZonaInmueble  en el contexto de Conjuntos Residenciales.</t>
+  </si>
+  <si>
+    <t>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</t>
+  </si>
+  <si>
+    <t>No pueden ser fechas futuras.</t>
+  </si>
+  <si>
+    <t>Sólo letras y números.</t>
   </si>
 </sst>
 </file>
@@ -2779,7 +2836,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2899,9 +2956,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2983,6 +3037,30 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3004,12 +3082,213 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3052,287 +3331,62 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3726,10 +3780,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
+      <c r="B1" s="79"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3839,11 +3893,11 @@
       <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="74"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
@@ -3861,15 +3915,15 @@
     </row>
     <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="75" t="str">
+      <c r="D3" s="82" t="str">
         <f>$B$1</f>
         <v>Agendas</v>
       </c>
@@ -3879,24 +3933,24 @@
         <v>20</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="76"/>
+      <c r="D4" s="83"/>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="77"/>
+      <c r="D5" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3943,73 +3997,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="88" t="str">
+      <c r="B2" s="162" t="str">
         <f>'Listado Objetos de Dominio'!A3</f>
         <v>Reserva</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="162"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="89" t="str">
+      <c r="B3" s="163" t="str">
         <f>'Listado Objetos de Dominio'!B3</f>
         <v>Corresponde a cada una de las reservas que pude hacer el residente, es decir, el residente puede reservar una zona común, ejemplo: El residente 001 reserva la piscina con su respectivo turno.</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -4063,18 +4117,18 @@
       <c r="Q4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="S4" s="65" t="str">
+      <c r="R4" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="S4" s="64" t="str">
         <f>A22</f>
         <v>Buscar</v>
       </c>
-      <c r="T4" s="66" t="str">
+      <c r="T4" s="65" t="str">
         <f>A23</f>
         <v>Modificar</v>
       </c>
-      <c r="U4" s="67" t="str">
+      <c r="U4" s="66" t="str">
         <f>A25</f>
         <v>Eliminar</v>
       </c>
@@ -4117,27 +4171,27 @@
         <v>43</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" s="68" t="s">
-        <v>157</v>
+        <v>85</v>
+      </c>
+      <c r="R5" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -4146,7 +4200,7 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J6" s="19"/>
       <c r="K6" s="21"/>
@@ -4166,24 +4220,24 @@
         <v>44</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="R6" s="68" t="s">
-        <v>157</v>
+        <v>86</v>
+      </c>
+      <c r="R6" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>20</v>
@@ -4213,27 +4267,27 @@
         <v>44</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="R7" s="68" t="s">
-        <v>157</v>
+        <v>83</v>
+      </c>
+      <c r="R7" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S7" s="35" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -4260,105 +4314,105 @@
         <v>44</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="R8" s="68" t="s">
-        <v>157</v>
+        <v>84</v>
+      </c>
+      <c r="R8" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S8" s="35" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="84" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="86"/>
+      <c r="A10" s="158" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="159"/>
+      <c r="C10" s="160"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="164" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="166" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="92" t="s">
-        <v>89</v>
-      </c>
       <c r="C12" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="91"/>
-      <c r="B13" s="93"/>
+      <c r="A13" s="165"/>
+      <c r="B13" s="167"/>
       <c r="C13" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="106" t="s">
+      <c r="A15" s="146" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="147"/>
+      <c r="C15" s="150" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="147"/>
+      <c r="H15" s="143" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="107"/>
-      <c r="C15" s="110" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="78" t="s">
+      <c r="I15" s="144"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="143" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="105"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="78" t="s">
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="145"/>
+      <c r="P15" s="143" t="s">
         <v>52</v>
       </c>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="79"/>
-      <c r="P15" s="78" t="s">
+      <c r="Q15" s="145"/>
+      <c r="R15" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="Q15" s="79"/>
-      <c r="R15" s="78" t="s">
+      <c r="S15" s="154"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="148"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="S15" s="80"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="108"/>
-      <c r="B16" s="109"/>
-      <c r="C16" s="112"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="46" t="s">
+      <c r="I16" s="32" t="s">
         <v>55</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>56</v>
       </c>
       <c r="J16" s="32" t="s">
         <v>2</v>
@@ -4366,200 +4420,200 @@
       <c r="K16" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="81" t="s">
+      <c r="L16" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="83"/>
+      <c r="M16" s="156"/>
+      <c r="N16" s="156"/>
+      <c r="O16" s="157"/>
       <c r="P16" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q16" s="32" t="s">
         <v>2</v>
       </c>
       <c r="R16" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="S16" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="S16" s="33" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="17" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="141" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="122" t="str">
+      <c r="A17" s="135" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="136"/>
+      <c r="C17" s="112" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="93" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I17" s="103" t="str">
+      <c r="I17" s="141" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
-      <c r="J17" s="122" t="str">
+      <c r="J17" s="93" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",$B$2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Reserva</v>
       </c>
-      <c r="K17" s="47"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="151"/>
-      <c r="N17" s="151"/>
-      <c r="O17" s="152"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="123"/>
       <c r="P17" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="S17" s="47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="137"/>
+      <c r="B18" s="138"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="142"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="125"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="S18" s="47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="137"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="125"/>
+      <c r="N19" s="125"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q19" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="Q17" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="S17" s="48" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
-      <c r="B18" s="100"/>
-      <c r="C18" s="144"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="145"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="146"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="153"/>
-      <c r="M18" s="154"/>
-      <c r="N18" s="154"/>
-      <c r="O18" s="155"/>
-      <c r="P18" s="14" t="s">
+      <c r="R19" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="S19" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="137"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="124"/>
+      <c r="M20" s="125"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="126"/>
+      <c r="P20" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q20" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="Q18" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="R18" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="S18" s="48" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="146"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="123"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="153"/>
-      <c r="M19" s="154"/>
-      <c r="N19" s="154"/>
-      <c r="O19" s="155"/>
-      <c r="P19" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q19" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="R19" s="13" t="s">
+      <c r="R20" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="S20" s="47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="139"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="S21" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="128"/>
+      <c r="C22" s="129" t="s">
         <v>177</v>
       </c>
-      <c r="S19" s="48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="144"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="145"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="146"/>
-      <c r="H20" s="123"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="153"/>
-      <c r="M20" s="154"/>
-      <c r="N20" s="154"/>
-      <c r="O20" s="155"/>
-      <c r="P20" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q20" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="R20" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="S20" s="48" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="101"/>
-      <c r="B21" s="102"/>
-      <c r="C21" s="147"/>
-      <c r="D21" s="148"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="124"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="124"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="S21" s="48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="156" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="157"/>
-      <c r="C22" s="158" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="159"/>
-      <c r="G22" s="160"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="131"/>
       <c r="H22" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I22" s="59" t="str">
+      <c r="I22" s="58" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
@@ -4567,111 +4621,111 @@
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de una  ",$B$2," en un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de una  Reserva en un conjunto residencial.</v>
       </c>
-      <c r="K22" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="L22" s="94" t="s">
-        <v>193</v>
-      </c>
-      <c r="M22" s="95"/>
-      <c r="N22" s="95"/>
-      <c r="O22" s="96"/>
+      <c r="K22" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="L22" s="132" t="s">
+        <v>185</v>
+      </c>
+      <c r="M22" s="133"/>
+      <c r="N22" s="133"/>
+      <c r="O22" s="134"/>
       <c r="P22" s="23" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="Q22" s="35" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="R22" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="S22" s="60" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="S22" s="59" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="137" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="138"/>
-      <c r="C23" s="125" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="133" t="str">
+      <c r="A23" s="108" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="109"/>
+      <c r="C23" s="96" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" s="97"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="104" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I23" s="135" t="str">
+      <c r="I23" s="106" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
-      <c r="J23" s="133" t="str">
+      <c r="J23" s="104" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar de la ",$B$2)</f>
         <v>Corresponde a los datos que se van a modificar de la Reserva</v>
       </c>
-      <c r="K23" s="131"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="126"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="61" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q23" s="62" t="s">
-        <v>152</v>
-      </c>
-      <c r="R23" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="S23" s="63" t="s">
-        <v>154</v>
+      <c r="K23" s="102"/>
+      <c r="L23" s="96"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="97"/>
+      <c r="O23" s="98"/>
+      <c r="P23" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q23" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="R23" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="S23" s="62" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="139"/>
-      <c r="B24" s="140"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="134"/>
-      <c r="I24" s="136"/>
-      <c r="J24" s="134"/>
-      <c r="K24" s="132"/>
-      <c r="L24" s="128"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="129"/>
-      <c r="O24" s="130"/>
-      <c r="P24" s="61" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q24" s="62" t="s">
-        <v>175</v>
-      </c>
-      <c r="R24" s="62" t="s">
-        <v>178</v>
-      </c>
-      <c r="S24" s="69" t="s">
-        <v>129</v>
+      <c r="A24" s="110"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="100"/>
+      <c r="N24" s="100"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q24" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="R24" s="61" t="s">
+        <v>170</v>
+      </c>
+      <c r="S24" s="68" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="114" t="s">
-        <v>155</v>
-      </c>
-      <c r="B25" s="115"/>
-      <c r="C25" s="116" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="118"/>
+      <c r="A25" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="86"/>
+      <c r="C25" s="87" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="89"/>
       <c r="H25" s="39" t="s">
         <v>41</v>
       </c>
@@ -4683,25 +4737,41 @@
         <v>Corresponde al identificador de la Reserva  que se quiere dar de baja.</v>
       </c>
       <c r="K25" s="40"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="120"/>
-      <c r="N25" s="120"/>
-      <c r="O25" s="121"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="92"/>
       <c r="P25" s="25" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="Q25" s="41" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="R25" s="41" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="S25" s="41" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="A17:B21"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="K15:O15"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:G16"/>
+    <mergeCell ref="H15:J15"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="L25:O25"/>
@@ -4718,22 +4788,6 @@
     <mergeCell ref="L17:O20"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:G22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="A17:B21"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:G16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -4762,10 +4816,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037CC029-DC44-4605-90F4-CA51C57B9385}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="8" customWidth="1"/>
     <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
@@ -4791,73 +4845,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="88" t="str">
+      <c r="B2" s="162" t="str">
         <f>'Listado Objetos de Dominio'!A5</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="162"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="89" t="str">
+      <c r="B3" s="163" t="str">
         <f>'Listado Objetos de Dominio'!B5</f>
         <v>Corresponde a la persona que puede realizar una reserva para una zona común.</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -4911,25 +4965,25 @@
       <c r="Q4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="S4" s="65" t="str">
-        <f>A30</f>
+      <c r="R4" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="S4" s="64" t="str">
+        <f>A39</f>
         <v>Buscar</v>
       </c>
-      <c r="T4" s="66" t="str">
-        <f>A31</f>
+      <c r="T4" s="65" t="str">
+        <f>A40</f>
         <v>Modificar</v>
       </c>
-      <c r="U4" s="67" t="str">
-        <f>A32</f>
+      <c r="U4" s="66" t="str">
+        <f>A41</f>
         <v>Eliminar</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
-        <v>41</v>
+      <c r="A5" s="26" t="s">
+        <v>241</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>9</v>
@@ -4965,24 +5019,24 @@
         <v>43</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="R5" s="68" t="s">
-        <v>157</v>
+        <v>91</v>
+      </c>
+      <c r="R5" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
-        <v>45</v>
+        <v>242</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>8</v>
@@ -4998,11 +5052,11 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J6" s="19"/>
       <c r="K6" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L6" s="22" t="s">
         <v>44</v>
@@ -5020,24 +5074,24 @@
         <v>44</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="R6" s="68" t="s">
-        <v>157</v>
+        <v>92</v>
+      </c>
+      <c r="R6" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>94</v>
+        <v>243</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>8</v>
@@ -5053,11 +5107,11 @@
       <c r="G7" s="19"/>
       <c r="H7" s="19"/>
       <c r="I7" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L7" s="22" t="s">
         <v>44</v>
@@ -5075,24 +5129,24 @@
         <v>44</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="R7" s="68" t="s">
-        <v>157</v>
+        <v>93</v>
+      </c>
+      <c r="R7" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>8</v>
@@ -5108,11 +5162,11 @@
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J8" s="19"/>
       <c r="K8" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L8" s="22" t="s">
         <v>44</v>
@@ -5130,24 +5184,24 @@
         <v>44</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="R8" s="68" t="s">
-        <v>157</v>
+        <v>95</v>
+      </c>
+      <c r="R8" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
-        <v>98</v>
+        <v>245</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>13</v>
@@ -5159,7 +5213,7 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
@@ -5179,24 +5233,24 @@
         <v>44</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="R9" s="68" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="R9" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U9" s="25" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>11</v>
@@ -5208,10 +5262,12 @@
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
       <c r="I10" s="20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J10" s="19"/>
-      <c r="K10" s="21"/>
+      <c r="K10" s="21" t="s">
+        <v>266</v>
+      </c>
       <c r="L10" s="19" t="s">
         <v>44</v>
       </c>
@@ -5228,24 +5284,24 @@
         <v>44</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="R10" s="68" t="s">
-        <v>157</v>
+        <v>100</v>
+      </c>
+      <c r="R10" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U10" s="25" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
-        <v>104</v>
+        <v>247</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>13</v>
@@ -5257,12 +5313,10 @@
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J11" s="19"/>
-      <c r="K11" s="21" t="s">
-        <v>60</v>
-      </c>
+      <c r="K11" s="21"/>
       <c r="L11" s="22" t="s">
         <v>44</v>
       </c>
@@ -5279,24 +5333,24 @@
         <v>44</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="R11" s="68" t="s">
-        <v>157</v>
+        <v>102</v>
+      </c>
+      <c r="R11" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U11" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
-        <v>106</v>
+        <v>248</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>9</v>
@@ -5312,11 +5366,11 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
       <c r="I12" s="20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L12" s="22" t="s">
         <v>44</v>
@@ -5334,24 +5388,24 @@
         <v>44</v>
       </c>
       <c r="Q12" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="R12" s="68" t="s">
-        <v>157</v>
+        <v>105</v>
+      </c>
+      <c r="R12" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U12" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="69" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
-        <v>109</v>
+        <v>249</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>9</v>
@@ -5367,11 +5421,11 @@
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J13" s="19"/>
       <c r="K13" s="21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L13" s="22" t="s">
         <v>44</v>
@@ -5389,36 +5443,40 @@
         <v>44</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="R13" s="68" t="s">
-        <v>157</v>
+        <v>108</v>
+      </c>
+      <c r="R13" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U13" s="25" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>113</v>
+        <v>250</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
+        <v>204</v>
+      </c>
+      <c r="C14" s="19">
+        <v>32</v>
+      </c>
+      <c r="D14" s="19">
+        <v>32</v>
+      </c>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="20" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="J14" s="19"/>
       <c r="K14" s="21"/>
@@ -5435,558 +5493,972 @@
         <v>44</v>
       </c>
       <c r="P14" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q14" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="R14" s="67"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="25"/>
+    </row>
+    <row r="15" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19">
+        <v>50</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="19"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q15" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="R15" s="67"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="25"/>
+    </row>
+    <row r="16" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="19">
+        <v>32</v>
+      </c>
+      <c r="D16" s="19">
+        <v>32</v>
+      </c>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="19"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="R16" s="67"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="25"/>
+    </row>
+    <row r="17" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19">
+        <v>50</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="J17" s="19"/>
+      <c r="K17" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O17" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="R17" s="67"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="25"/>
+    </row>
+    <row r="18" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="19">
+        <v>32</v>
+      </c>
+      <c r="D18" s="19">
+        <v>32</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="19"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="R18" s="67"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="25"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="19">
+        <v>20</v>
+      </c>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19">
+        <v>1</v>
+      </c>
+      <c r="H19" s="19">
+        <v>200</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="19"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="R19" s="67"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="25"/>
+    </row>
+    <row r="20" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="19">
+        <v>32</v>
+      </c>
+      <c r="D20" s="19">
+        <v>32</v>
+      </c>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="R20" s="67"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="25"/>
+    </row>
+    <row r="21" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="19">
+        <v>1</v>
+      </c>
+      <c r="D21" s="19">
+        <v>50</v>
+      </c>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="K21" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O21" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q21" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="R21" s="67"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="24"/>
+      <c r="U21" s="25"/>
+    </row>
+    <row r="22" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="19">
+        <v>32</v>
+      </c>
+      <c r="D22" s="19">
+        <v>32</v>
+      </c>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="19"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O22" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="R22" s="67"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="24"/>
+      <c r="U22" s="25"/>
+    </row>
+    <row r="23" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="19">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19">
+        <v>50</v>
+      </c>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="J23" s="19"/>
+      <c r="K23" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="O23" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P23" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q23" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="R23" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="S23" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="T23" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="U23" s="25" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="181" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="181"/>
+      <c r="C25" s="181"/>
+      <c r="E25" s="181" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="181"/>
+      <c r="G25" s="181"/>
+      <c r="I25" s="181" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="181"/>
+      <c r="K25" s="181"/>
+    </row>
+    <row r="26" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" s="28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="179" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="180" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="178" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="180" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="180" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="178" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="43"/>
+      <c r="I27" s="179" t="s">
+        <v>114</v>
+      </c>
+      <c r="J27" s="180" t="s">
+        <v>115</v>
+      </c>
+      <c r="K27" s="178" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="179"/>
+      <c r="B28" s="180"/>
+      <c r="C28" s="178"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="180"/>
+      <c r="G28" s="178"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="179"/>
+      <c r="J28" s="180"/>
+      <c r="K28" s="178"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="179"/>
+      <c r="B29" s="180"/>
+      <c r="C29" s="178" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="180"/>
+      <c r="F29" s="180"/>
+      <c r="G29" s="178"/>
+      <c r="I29" s="179"/>
+      <c r="J29" s="180"/>
+      <c r="K29" s="178"/>
+    </row>
+    <row r="30" spans="1:21" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="179"/>
+      <c r="B30" s="180"/>
+      <c r="C30" s="178"/>
+      <c r="E30" s="180"/>
+      <c r="F30" s="180"/>
+      <c r="G30" s="178"/>
+      <c r="I30" s="179"/>
+      <c r="J30" s="180"/>
+      <c r="K30" s="178"/>
+    </row>
+    <row r="31" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="146" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="147"/>
+      <c r="C32" s="150" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="151"/>
+      <c r="E32" s="151"/>
+      <c r="F32" s="151"/>
+      <c r="G32" s="147"/>
+      <c r="H32" s="143" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" s="144"/>
+      <c r="J32" s="145"/>
+      <c r="K32" s="143" t="s">
+        <v>51</v>
+      </c>
+      <c r="L32" s="144"/>
+      <c r="M32" s="144"/>
+      <c r="N32" s="144"/>
+      <c r="O32" s="145"/>
+      <c r="P32" s="143" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q32" s="145"/>
+      <c r="R32" s="143" t="s">
+        <v>53</v>
+      </c>
+      <c r="S32" s="154"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="148"/>
+      <c r="B33" s="149"/>
+      <c r="C33" s="152"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J33" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K33" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="M33" s="156"/>
+      <c r="N33" s="156"/>
+      <c r="O33" s="157"/>
+      <c r="P33" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q33" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="R33" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="S33" s="33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="135" t="s">
         <v>116</v>
       </c>
-      <c r="R14" s="68" t="s">
-        <v>157</v>
-      </c>
-      <c r="S14" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="T14" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="U14" s="25" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="161" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="161"/>
-      <c r="C16" s="161"/>
-      <c r="E16" s="161" t="s">
+      <c r="B34" s="136"/>
+      <c r="C34" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="161"/>
-      <c r="G16" s="161"/>
-      <c r="I16" s="161" t="s">
-        <v>47</v>
-      </c>
-      <c r="J16" s="161"/>
-      <c r="K16" s="161"/>
-    </row>
-    <row r="17" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="162" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="163" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="164" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="163" t="s">
-        <v>120</v>
-      </c>
-      <c r="F18" s="163" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="164" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="162" t="s">
-        <v>122</v>
-      </c>
-      <c r="J18" s="163" t="s">
-        <v>123</v>
-      </c>
-      <c r="K18" s="164" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="162"/>
-      <c r="B19" s="163"/>
-      <c r="C19" s="164"/>
-      <c r="E19" s="163"/>
-      <c r="F19" s="163"/>
-      <c r="G19" s="164"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="162"/>
-      <c r="J19" s="163"/>
-      <c r="K19" s="164"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="162"/>
-      <c r="B20" s="163"/>
-      <c r="C20" s="164" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="163"/>
-      <c r="F20" s="163"/>
-      <c r="G20" s="164"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="163"/>
-      <c r="K20" s="164"/>
-    </row>
-    <row r="21" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="162"/>
-      <c r="B21" s="163"/>
-      <c r="C21" s="164"/>
-      <c r="E21" s="163"/>
-      <c r="F21" s="163"/>
-      <c r="G21" s="164"/>
-      <c r="I21" s="162"/>
-      <c r="J21" s="163"/>
-      <c r="K21" s="164"/>
-    </row>
-    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="106" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="107"/>
-      <c r="C23" s="110" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="78" t="s">
-        <v>51</v>
-      </c>
-      <c r="I23" s="105"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="78" t="s">
-        <v>52</v>
-      </c>
-      <c r="L23" s="105"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="105"/>
-      <c r="O23" s="79"/>
-      <c r="P23" s="78" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q23" s="79"/>
-      <c r="R23" s="78" t="s">
-        <v>54</v>
-      </c>
-      <c r="S23" s="80"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="108"/>
-      <c r="B24" s="109"/>
-      <c r="C24" s="112"/>
-      <c r="D24" s="113"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J24" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K24" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="81" t="s">
-        <v>2</v>
-      </c>
-      <c r="M24" s="82"/>
-      <c r="N24" s="82"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q24" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="R24" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="S24" s="33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="141" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="142"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="122" t="str">
+      <c r="D34" s="113"/>
+      <c r="E34" s="113"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="114"/>
+      <c r="H34" s="93" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I25" s="103" t="str">
+      <c r="I34" s="141" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J25" s="173" t="str">
+      <c r="J34" s="176" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Residente</v>
       </c>
-      <c r="K25" s="47"/>
-      <c r="L25" s="150"/>
-      <c r="M25" s="151"/>
-      <c r="N25" s="151"/>
-      <c r="O25" s="152"/>
-      <c r="P25" s="14" t="s">
+      <c r="K34" s="46"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="122"/>
+      <c r="N34" s="122"/>
+      <c r="O34" s="123"/>
+      <c r="P34" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q34" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="R34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="S34" s="47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="137"/>
+      <c r="B35" s="138"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="116"/>
+      <c r="E35" s="116"/>
+      <c r="F35" s="116"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="142"/>
+      <c r="J35" s="177"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="124"/>
+      <c r="M35" s="125"/>
+      <c r="N35" s="125"/>
+      <c r="O35" s="126"/>
+      <c r="P35" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q35" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="R35" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="S35" s="47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="137"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="115"/>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="116"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="94"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="177"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="124"/>
+      <c r="M36" s="125"/>
+      <c r="N36" s="125"/>
+      <c r="O36" s="126"/>
+      <c r="P36" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q36" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="Q25" s="13" t="s">
+      <c r="R36" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="R25" s="13" t="s">
+      <c r="S36" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="S25" s="48" t="s">
+    </row>
+    <row r="37" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="137"/>
+      <c r="B37" s="138"/>
+      <c r="C37" s="115"/>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="116"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="94"/>
+      <c r="I37" s="142"/>
+      <c r="J37" s="177"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="124"/>
+      <c r="M37" s="125"/>
+      <c r="N37" s="125"/>
+      <c r="O37" s="126"/>
+      <c r="P37" s="14" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="99"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="145"/>
-      <c r="E26" s="145"/>
-      <c r="F26" s="145"/>
-      <c r="G26" s="146"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="174"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="153"/>
-      <c r="M26" s="154"/>
-      <c r="N26" s="154"/>
-      <c r="O26" s="155"/>
-      <c r="P26" s="14" t="s">
+      <c r="Q37" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="Q26" s="13" t="s">
+      <c r="R37" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="R26" s="13" t="s">
+      <c r="S37" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="S26" s="48" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="99"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="144"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="145"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="146"/>
-      <c r="H27" s="123"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="174"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="153"/>
-      <c r="M27" s="154"/>
-      <c r="N27" s="154"/>
-      <c r="O27" s="155"/>
-      <c r="P27" s="14" t="s">
+    </row>
+    <row r="38" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="139"/>
+      <c r="B38" s="140"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="Q27" s="13" t="s">
+      <c r="Q38" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="R27" s="13" t="s">
+      <c r="R38" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="S27" s="48" t="s">
+      <c r="S38" s="47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="127" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="99"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="144"/>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="146"/>
-      <c r="H28" s="123"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="174"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="154"/>
-      <c r="N28" s="154"/>
-      <c r="O28" s="155"/>
-      <c r="P28" s="14" t="s">
+      <c r="B39" s="128"/>
+      <c r="C39" s="129" t="s">
         <v>137</v>
       </c>
-      <c r="Q28" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="R28" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="S28" s="48" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="101"/>
-      <c r="B29" s="102"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q29" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="R29" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="S29" s="48" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="156" t="s">
-        <v>144</v>
-      </c>
-      <c r="B30" s="157"/>
-      <c r="C30" s="158" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="159"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="34" t="str">
+      <c r="D39" s="130"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I30" s="59" t="str">
+      <c r="I39" s="58" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J30" s="34" t="str">
+      <c r="J39" s="34" t="str">
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de un  ",B2," de un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de un  Residente de un conjunto residencial.</v>
       </c>
-      <c r="K30" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="L30" s="94" t="s">
-        <v>165</v>
-      </c>
-      <c r="M30" s="95"/>
-      <c r="N30" s="95"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q30" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="R30" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="S30" s="60" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="165" t="s">
-        <v>149</v>
-      </c>
-      <c r="B31" s="166"/>
-      <c r="C31" s="167" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="168"/>
-      <c r="E31" s="168"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="169"/>
-      <c r="H31" s="36" t="str">
+      <c r="K39" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="L39" s="132" t="s">
+        <v>157</v>
+      </c>
+      <c r="M39" s="133"/>
+      <c r="N39" s="133"/>
+      <c r="O39" s="134"/>
+      <c r="P39" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q39" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="R39" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="S39" s="59" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="168" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="169"/>
+      <c r="C40" s="170" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="171"/>
+      <c r="E40" s="171"/>
+      <c r="F40" s="171"/>
+      <c r="G40" s="172"/>
+      <c r="H40" s="36" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I31" s="37" t="str">
+      <c r="I40" s="37" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J31" s="36" t="str">
+      <c r="J40" s="36" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar del ",B2)</f>
         <v>Corresponde a los datos que se van a modificar del Residente</v>
       </c>
-      <c r="K31" s="38"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="171"/>
-      <c r="N31" s="171"/>
-      <c r="O31" s="172"/>
-      <c r="P31" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q31" s="62" t="s">
-        <v>152</v>
-      </c>
-      <c r="R31" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="S31" s="63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="114" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="115"/>
-      <c r="C32" s="116" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="39" t="s">
+      <c r="K40" s="38"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="174"/>
+      <c r="N40" s="174"/>
+      <c r="O40" s="175"/>
+      <c r="P40" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q40" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="R40" s="61" t="s">
+        <v>145</v>
+      </c>
+      <c r="S40" s="62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="86"/>
+      <c r="C41" s="87" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="25" t="s">
+      <c r="I41" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="39" t="str">
+      <c r="J41" s="39" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
-      <c r="K32" s="40"/>
-      <c r="L32" s="119"/>
-      <c r="M32" s="120"/>
-      <c r="N32" s="120"/>
-      <c r="O32" s="121"/>
-      <c r="P32" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q32" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="R32" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="S32" s="41" t="s">
-        <v>154</v>
+      <c r="K41" s="40"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="91"/>
+      <c r="N41" s="91"/>
+      <c r="O41" s="92"/>
+      <c r="P41" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q41" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="R41" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="S41" s="41" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="A25:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="C25:G28"/>
-    <mergeCell ref="H25:H28"/>
-    <mergeCell ref="I25:I28"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="L25:O28"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:G24"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:O23"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="J18:J21"/>
-    <mergeCell ref="K18:K21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="F18:F21"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="F27:F30"/>
+    <mergeCell ref="G27:G30"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="J27:J30"/>
+    <mergeCell ref="K27:K30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="C32:G33"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="K32:O32"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="L41:O41"/>
+    <mergeCell ref="A34:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="L40:O40"/>
+    <mergeCell ref="C34:G37"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="J34:J37"/>
+    <mergeCell ref="L34:O37"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{1AE4FE85-AF13-4BAA-9ECE-73FAE508027B}"/>
     <hyperlink ref="A1:Q1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{3716152C-292E-417A-893F-424864CE08BA}"/>
-    <hyperlink ref="C20" location="Residente!A9" display="numeroDocumento" xr:uid="{DFCD61D0-5CB4-4F8F-985B-694C43E6EA19}"/>
+    <hyperlink ref="C29" location="Residente!A9" display="numeroDocumento" xr:uid="{DFCD61D0-5CB4-4F8F-985B-694C43E6EA19}"/>
     <hyperlink ref="I12" r:id="rId1" xr:uid="{7F566C26-F907-47F3-8B5D-824A88113FE0}"/>
-    <hyperlink ref="A5" location="Residente!A12" display="identificador" xr:uid="{446BB3D6-88B2-4F9C-95E4-D1AA3DFC372C}"/>
-    <hyperlink ref="C18" location="Residente!A8" display="tipoDocumento" xr:uid="{3FA7C9E7-8C14-4BF0-9758-F62697ABA7B6}"/>
-    <hyperlink ref="G18:G21" location="Residente!A11" display="numeroContacto" xr:uid="{FA4FEAA1-EEB9-4FA7-82E0-963F9C3B1C2F}"/>
-    <hyperlink ref="K18:K21" location="Residente!A12" display="correoElectronico" xr:uid="{50DD6B65-8045-4E42-A131-3642AA5EA6CD}"/>
-    <hyperlink ref="I32" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{497DD431-A160-4450-A870-D95845AF6337}"/>
-    <hyperlink ref="A30:B30" location="Residente!S4" display="Buscar" xr:uid="{ABA9C985-BA56-439E-8A7A-A6B65FB1418E}"/>
-    <hyperlink ref="A32:B32" location="Residente!U4" display="Eliminar" xr:uid="{0A6FE94D-C425-4C6C-BDC7-52549C31DE3F}"/>
-    <hyperlink ref="A31:B31" location="Residente!T4" display="Modificar" xr:uid="{6116F882-5711-4F36-BE4A-43FB1CB04042}"/>
-    <hyperlink ref="I25:I28" location="Residente!B2" display="Residente!B2" xr:uid="{570CC34F-7D11-4CD7-98B4-381DCC330A61}"/>
-    <hyperlink ref="I30" location="Residente!B2" display="Residente!B2" xr:uid="{630FABF8-71A5-4CD4-A861-4C7E37773599}"/>
-    <hyperlink ref="I31" location="Residente!B2" display="Residente!B2" xr:uid="{69B9D49B-88A1-4AE6-92D6-6C29739F94CE}"/>
+    <hyperlink ref="C27" location="Residente!A8" display="tipoDocumento" xr:uid="{3FA7C9E7-8C14-4BF0-9758-F62697ABA7B6}"/>
+    <hyperlink ref="G27:G30" location="Residente!A11" display="numeroContacto" xr:uid="{FA4FEAA1-EEB9-4FA7-82E0-963F9C3B1C2F}"/>
+    <hyperlink ref="K27:K30" location="Residente!A12" display="correoElectronico" xr:uid="{50DD6B65-8045-4E42-A131-3642AA5EA6CD}"/>
+    <hyperlink ref="I41" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{497DD431-A160-4450-A870-D95845AF6337}"/>
+    <hyperlink ref="A39:B39" location="Residente!S4" display="Buscar" xr:uid="{ABA9C985-BA56-439E-8A7A-A6B65FB1418E}"/>
+    <hyperlink ref="A41:B41" location="Residente!U4" display="Eliminar" xr:uid="{0A6FE94D-C425-4C6C-BDC7-52549C31DE3F}"/>
+    <hyperlink ref="A40:B40" location="Residente!T4" display="Modificar" xr:uid="{6116F882-5711-4F36-BE4A-43FB1CB04042}"/>
+    <hyperlink ref="I34:I37" location="Residente!B2" display="Residente!B2" xr:uid="{570CC34F-7D11-4CD7-98B4-381DCC330A61}"/>
+    <hyperlink ref="I39" location="Residente!B2" display="Residente!B2" xr:uid="{630FABF8-71A5-4CD4-A861-4C7E37773599}"/>
+    <hyperlink ref="I40" location="Residente!B2" display="Residente!B2" xr:uid="{69B9D49B-88A1-4AE6-92D6-6C29739F94CE}"/>
     <hyperlink ref="T4" location="Residente!A31" display="Residente!A31" xr:uid="{A80BF91E-B916-4AAC-8A53-FAD7D15EF18A}"/>
     <hyperlink ref="U4" location="Residente!A32" display="Residente!A32" xr:uid="{1EF9E111-39FA-4471-B740-CA2579CB32F5}"/>
     <hyperlink ref="R4" location="Residente!A25" display="Registrar" xr:uid="{33F13131-C39E-4548-B53E-38537739A002}"/>
     <hyperlink ref="S4" location="Residente!A30" display="Residente!A30" xr:uid="{F5C98B1D-D86B-41BC-B213-515A1D283A7B}"/>
-    <hyperlink ref="A25:B29" location="Residente!R4" display="Registrar" xr:uid="{425D74EB-77D6-43A9-AC59-69DE19D482EF}"/>
+    <hyperlink ref="A34:B38" location="Residente!R4" display="Registrar" xr:uid="{425D74EB-77D6-43A9-AC59-69DE19D482EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
@@ -6008,7 +6480,7 @@
     <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
     <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30" style="180" customWidth="1"/>
+    <col min="11" max="11" width="30" style="70" customWidth="1"/>
     <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -6024,73 +6496,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="88" t="str">
+      <c r="B2" s="162" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Turno</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="162"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="89" t="str">
+      <c r="B3" s="163" t="str">
         <f>'Listado Objetos de Dominio'!B4</f>
         <v>Corresponde a los turnos que un residente puede reservar en una agenda, es decir, el residente toma un turno que esta disponible de una agenda que anteriormente ya esta programada.</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -6144,25 +6616,25 @@
       <c r="Q4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="S4" s="65" t="str">
+      <c r="R4" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="S4" s="64" t="str">
         <f>A39</f>
         <v>Buscar</v>
       </c>
-      <c r="T4" s="66" t="str">
+      <c r="T4" s="65" t="str">
         <f>A40</f>
         <v>Modificar</v>
       </c>
-      <c r="U4" s="67" t="str">
+      <c r="U4" s="66" t="str">
         <f>A41</f>
         <v>Eliminar</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>9</v>
@@ -6178,7 +6650,7 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
       <c r="I5" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="21"/>
@@ -6198,24 +6670,24 @@
         <v>43</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="R5" s="68" t="s">
-        <v>157</v>
+        <v>70</v>
+      </c>
+      <c r="R5" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>8</v>
@@ -6231,7 +6703,7 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J6" s="19"/>
       <c r="K6" s="21"/>
@@ -6251,27 +6723,27 @@
         <v>44</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="R6" s="68" t="s">
-        <v>157</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -6280,11 +6752,11 @@
       <c r="G7" s="19"/>
       <c r="H7" s="19"/>
       <c r="I7" s="20" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="21" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L7" s="22" t="s">
         <v>44</v>
@@ -6302,23 +6774,23 @@
         <v>44</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="R7" s="68" t="s">
-        <v>157</v>
+        <v>72</v>
+      </c>
+      <c r="R7" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S7" s="23"/>
       <c r="T7" s="24"/>
       <c r="U7" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -6327,11 +6799,11 @@
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="20" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J8" s="19"/>
       <c r="K8" s="21" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L8" s="22" t="s">
         <v>44</v>
@@ -6349,23 +6821,23 @@
         <v>44</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="R8" s="68" t="s">
-        <v>157</v>
+        <v>73</v>
+      </c>
+      <c r="R8" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S8" s="23"/>
       <c r="T8" s="24"/>
       <c r="U8" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -6374,7 +6846,7 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="20" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="21"/>
@@ -6394,20 +6866,20 @@
         <v>44</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="R9" s="68" t="s">
-        <v>157</v>
+        <v>74</v>
+      </c>
+      <c r="R9" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S9" s="23"/>
       <c r="T9" s="24"/>
       <c r="U9" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>9</v>
@@ -6423,7 +6895,7 @@
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
       <c r="I10" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="20"/>
@@ -6443,20 +6915,20 @@
         <v>44</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="R10" s="68" t="s">
-        <v>157</v>
+        <v>225</v>
+      </c>
+      <c r="R10" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S10" s="35"/>
       <c r="T10" s="24"/>
       <c r="U10" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>8</v>
@@ -6472,11 +6944,11 @@
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="21" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L11" s="22" t="s">
         <v>44</v>
@@ -6494,23 +6966,23 @@
         <v>44</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="R11" s="68" t="s">
-        <v>157</v>
+        <v>226</v>
+      </c>
+      <c r="R11" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S11" s="35"/>
       <c r="T11" s="24"/>
       <c r="U11" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
@@ -6519,7 +6991,7 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
       <c r="I12" s="20" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="20"/>
@@ -6539,23 +7011,23 @@
         <v>44</v>
       </c>
       <c r="Q12" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="R12" s="68" t="s">
-        <v>157</v>
+        <v>227</v>
+      </c>
+      <c r="R12" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S12" s="35"/>
       <c r="T12" s="24"/>
       <c r="U12" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
@@ -6564,11 +7036,11 @@
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="20" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J13" s="19"/>
       <c r="K13" s="21" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L13" s="22" t="s">
         <v>44</v>
@@ -6586,23 +7058,23 @@
         <v>44</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="R13" s="68" t="s">
-        <v>157</v>
+        <v>228</v>
+      </c>
+      <c r="R13" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S13" s="35"/>
       <c r="T13" s="24"/>
       <c r="U13" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -6611,11 +7083,11 @@
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="20" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J14" s="19"/>
       <c r="K14" s="21" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L14" s="22" t="s">
         <v>44</v>
@@ -6633,23 +7105,23 @@
         <v>44</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="R14" s="68" t="s">
-        <v>157</v>
+        <v>229</v>
+      </c>
+      <c r="R14" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S14" s="35"/>
       <c r="T14" s="24"/>
       <c r="U14" s="25" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" s="185" customFormat="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" s="75" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C15" s="19">
         <v>32</v>
@@ -6682,24 +7154,24 @@
         <v>43</v>
       </c>
       <c r="Q15" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="R15" s="68" t="s">
-        <v>157</v>
-      </c>
-      <c r="S15" s="186" t="s">
-        <v>160</v>
-      </c>
-      <c r="T15" s="187" t="s">
-        <v>161</v>
+        <v>230</v>
+      </c>
+      <c r="R15" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="S15" s="76" t="s">
+        <v>152</v>
+      </c>
+      <c r="T15" s="77" t="s">
+        <v>153</v>
       </c>
       <c r="U15" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A16" s="26" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>8</v>
@@ -6715,11 +7187,11 @@
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
       <c r="I16" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J16" s="19"/>
       <c r="K16" s="21" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L16" s="19" t="s">
         <v>44</v>
@@ -6737,23 +7209,23 @@
         <v>44</v>
       </c>
       <c r="Q16" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="R16" s="68" t="s">
-        <v>157</v>
+        <v>231</v>
+      </c>
+      <c r="R16" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S16" s="35"/>
       <c r="T16" s="24"/>
       <c r="U16" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>1</v>
@@ -6766,11 +7238,11 @@
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
       <c r="I17" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J17" s="19"/>
       <c r="K17" s="21" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L17" s="19" t="s">
         <v>44</v>
@@ -6788,20 +7260,20 @@
         <v>44</v>
       </c>
       <c r="Q17" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="R17" s="68" t="s">
-        <v>157</v>
+        <v>232</v>
+      </c>
+      <c r="R17" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S17" s="35"/>
       <c r="T17" s="24"/>
       <c r="U17" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>8</v>
@@ -6817,11 +7289,11 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J18" s="19"/>
       <c r="K18" s="21" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L18" s="19" t="s">
         <v>44</v>
@@ -6839,20 +7311,20 @@
         <v>44</v>
       </c>
       <c r="Q18" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="R18" s="68" t="s">
-        <v>157</v>
+        <v>233</v>
+      </c>
+      <c r="R18" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S18" s="35"/>
       <c r="T18" s="24"/>
       <c r="U18" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="26" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>8</v>
@@ -6868,11 +7340,11 @@
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
       <c r="I19" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J19" s="19"/>
       <c r="K19" s="21" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="L19" s="19" t="s">
         <v>44</v>
@@ -6890,23 +7362,23 @@
         <v>44</v>
       </c>
       <c r="Q19" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="R19" s="68" t="s">
-        <v>157</v>
+        <v>234</v>
+      </c>
+      <c r="R19" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S19" s="35"/>
       <c r="T19" s="24"/>
       <c r="U19" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="19">
         <v>1</v>
@@ -6923,11 +7395,11 @@
         <v>3600</v>
       </c>
       <c r="I20" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="21" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L20" s="19" t="s">
         <v>44</v>
@@ -6945,23 +7417,23 @@
         <v>44</v>
       </c>
       <c r="Q20" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="R20" s="68" t="s">
-        <v>157</v>
+        <v>235</v>
+      </c>
+      <c r="R20" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S20" s="35"/>
       <c r="T20" s="24"/>
       <c r="U20" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C21" s="19">
         <v>32</v>
@@ -6994,10 +7466,10 @@
         <v>43</v>
       </c>
       <c r="Q21" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="R21" s="68" t="s">
-        <v>157</v>
+        <v>236</v>
+      </c>
+      <c r="R21" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S21" s="35" t="str">
         <f>_xlfn.CONCAT(L21,$B$5)</f>
@@ -7008,12 +7480,12 @@
         <v>NoAlfanumerico</v>
       </c>
       <c r="U21" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>8</v>
@@ -7029,11 +7501,11 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="21" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L22" s="22" t="s">
         <v>44</v>
@@ -7051,24 +7523,24 @@
         <v>44</v>
       </c>
       <c r="Q22" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="R22" s="68" t="s">
-        <v>157</v>
+        <v>237</v>
+      </c>
+      <c r="R22" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S22" s="35" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U22" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>8</v>
@@ -7084,11 +7556,11 @@
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="20" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="21" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L23" s="22" t="s">
         <v>44</v>
@@ -7106,20 +7578,20 @@
         <v>44</v>
       </c>
       <c r="Q23" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="R23" s="68" t="s">
-        <v>157</v>
+        <v>238</v>
+      </c>
+      <c r="R23" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S23" s="35"/>
       <c r="T23" s="24"/>
       <c r="U23" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="26" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>10</v>
@@ -7135,7 +7607,7 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="20" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="J24" s="19"/>
       <c r="K24" s="21"/>
@@ -7155,23 +7627,23 @@
         <v>44</v>
       </c>
       <c r="Q24" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="R24" s="68" t="s">
-        <v>157</v>
+        <v>239</v>
+      </c>
+      <c r="R24" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S24" s="35"/>
       <c r="T24" s="24"/>
       <c r="U24" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A25" s="26" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C25" s="19">
         <v>32</v>
@@ -7204,20 +7676,20 @@
         <v>43</v>
       </c>
       <c r="Q25" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="R25" s="68" t="s">
-        <v>157</v>
+        <v>240</v>
+      </c>
+      <c r="R25" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S25" s="35"/>
       <c r="T25" s="24"/>
       <c r="U25" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>8</v>
@@ -7233,11 +7705,11 @@
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J26" s="19"/>
       <c r="K26" s="21" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L26" s="22" t="s">
         <v>44</v>
@@ -7255,224 +7727,224 @@
         <v>44</v>
       </c>
       <c r="Q26" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="R26" s="68" t="s">
-        <v>157</v>
+        <v>237</v>
+      </c>
+      <c r="R26" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="S26" s="35"/>
       <c r="T26" s="24"/>
       <c r="U26" s="25" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="84" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="85"/>
-      <c r="C28" s="86"/>
+      <c r="A28" s="158" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="159"/>
+      <c r="C28" s="160"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>2</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="90" t="s">
+      <c r="A30" s="164" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="166" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="92" t="s">
-        <v>91</v>
-      </c>
       <c r="C30" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="175"/>
-      <c r="B31" s="176"/>
+      <c r="A31" s="185"/>
+      <c r="B31" s="186"/>
       <c r="C31" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="185"/>
+      <c r="B32" s="186"/>
+      <c r="C32" s="30" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="175"/>
-      <c r="B32" s="176"/>
-      <c r="C32" s="30" t="s">
+    <row r="33" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="165"/>
+      <c r="B33" s="167"/>
+      <c r="C33" s="42" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="91"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="42" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A35" s="106" t="s">
+      <c r="A35" s="146" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="147"/>
+      <c r="C35" s="150" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="147"/>
+      <c r="H35" s="143" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="107"/>
-      <c r="C35" s="110" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="107"/>
-      <c r="H35" s="78" t="s">
+      <c r="I35" s="144"/>
+      <c r="J35" s="145"/>
+      <c r="K35" s="143" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="105"/>
-      <c r="J35" s="79"/>
-      <c r="K35" s="78" t="s">
+      <c r="L35" s="144"/>
+      <c r="M35" s="144"/>
+      <c r="N35" s="144"/>
+      <c r="O35" s="145"/>
+      <c r="P35" s="143" t="s">
         <v>52</v>
       </c>
-      <c r="L35" s="105"/>
-      <c r="M35" s="105"/>
-      <c r="N35" s="105"/>
-      <c r="O35" s="79"/>
-      <c r="P35" s="78" t="s">
+      <c r="Q35" s="145"/>
+      <c r="R35" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="Q35" s="79"/>
-      <c r="R35" s="78" t="s">
+      <c r="S35" s="154"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="148"/>
+      <c r="B36" s="149"/>
+      <c r="C36" s="152"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="149"/>
+      <c r="H36" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="S35" s="80"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A36" s="108"/>
-      <c r="B36" s="109"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
-      <c r="F36" s="113"/>
-      <c r="G36" s="109"/>
-      <c r="H36" s="46" t="s">
+      <c r="I36" s="32" t="s">
         <v>55</v>
-      </c>
-      <c r="I36" s="32" t="s">
-        <v>56</v>
       </c>
       <c r="J36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="K36" s="46" t="s">
+      <c r="K36" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="L36" s="81" t="s">
+      <c r="L36" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="M36" s="82"/>
-      <c r="N36" s="82"/>
-      <c r="O36" s="83"/>
+      <c r="M36" s="156"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="157"/>
       <c r="P36" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q36" s="32" t="s">
         <v>2</v>
       </c>
       <c r="R36" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="S36" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="S36" s="33" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="37" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" s="98"/>
-      <c r="C37" s="141" t="s">
-        <v>188</v>
-      </c>
-      <c r="D37" s="142"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="143"/>
-      <c r="H37" s="122" t="str">
+      <c r="A37" s="135" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="136"/>
+      <c r="C37" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="114"/>
+      <c r="H37" s="93" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
       </c>
-      <c r="I37" s="122" t="str">
+      <c r="I37" s="93" t="str">
         <f>B2</f>
         <v>Turno</v>
       </c>
-      <c r="J37" s="122" t="str">
+      <c r="J37" s="93" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",$B$2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Turno</v>
       </c>
-      <c r="K37" s="181"/>
-      <c r="L37" s="150"/>
-      <c r="M37" s="151"/>
-      <c r="N37" s="151"/>
-      <c r="O37" s="152"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="122"/>
+      <c r="N37" s="122"/>
+      <c r="O37" s="123"/>
       <c r="P37" s="14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="Q37" s="13" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="R37" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="S37" s="48" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="S37" s="47" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="99"/>
-      <c r="B38" s="100"/>
-      <c r="C38" s="144"/>
-      <c r="D38" s="145"/>
-      <c r="E38" s="145"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="146"/>
-      <c r="H38" s="123"/>
-      <c r="I38" s="123"/>
-      <c r="J38" s="123"/>
-      <c r="K38" s="182"/>
-      <c r="L38" s="153"/>
-      <c r="M38" s="154"/>
-      <c r="N38" s="154"/>
-      <c r="O38" s="155"/>
+      <c r="A38" s="137"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="115"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="116"/>
+      <c r="F38" s="116"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="94"/>
+      <c r="I38" s="94"/>
+      <c r="J38" s="94"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="124"/>
+      <c r="M38" s="125"/>
+      <c r="N38" s="125"/>
+      <c r="O38" s="126"/>
       <c r="P38" s="14" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="Q38" s="13" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="R38" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="S38" s="48" t="s">
-        <v>182</v>
+        <v>190</v>
+      </c>
+      <c r="S38" s="47" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="156" t="s">
-        <v>144</v>
-      </c>
-      <c r="B39" s="157"/>
-      <c r="C39" s="158" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="159"/>
-      <c r="E39" s="159"/>
-      <c r="F39" s="159"/>
-      <c r="G39" s="160"/>
+      <c r="A39" s="127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="128"/>
+      <c r="C39" s="129" t="s">
+        <v>181</v>
+      </c>
+      <c r="D39" s="130"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="131"/>
       <c r="H39" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
@@ -7485,82 +7957,82 @@
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de un  ",$B$2," en un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de un  Turno en un conjunto residencial.</v>
       </c>
-      <c r="K39" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="L39" s="94" t="s">
-        <v>194</v>
-      </c>
-      <c r="M39" s="95"/>
-      <c r="N39" s="95"/>
-      <c r="O39" s="96"/>
+      <c r="K39" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="L39" s="132" t="s">
+        <v>186</v>
+      </c>
+      <c r="M39" s="133"/>
+      <c r="N39" s="133"/>
+      <c r="O39" s="134"/>
       <c r="P39" s="23" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="Q39" s="35" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="R39" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="S39" s="60" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="S39" s="59" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="137" t="s">
-        <v>149</v>
-      </c>
-      <c r="B40" s="138"/>
-      <c r="C40" s="177" t="s">
-        <v>190</v>
-      </c>
-      <c r="D40" s="178"/>
-      <c r="E40" s="178"/>
-      <c r="F40" s="178"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="70" t="str">
+      <c r="A40" s="108" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="109"/>
+      <c r="C40" s="182" t="s">
+        <v>182</v>
+      </c>
+      <c r="D40" s="183"/>
+      <c r="E40" s="183"/>
+      <c r="F40" s="183"/>
+      <c r="G40" s="184"/>
+      <c r="H40" s="69" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
       </c>
-      <c r="I40" s="70" t="str">
+      <c r="I40" s="69" t="str">
         <f>B2</f>
         <v>Turno</v>
       </c>
-      <c r="J40" s="70" t="str">
+      <c r="J40" s="69" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar del ",$B$2)</f>
         <v>Corresponde a los datos que se van a modificar del Turno</v>
       </c>
-      <c r="K40" s="183"/>
-      <c r="L40" s="125"/>
-      <c r="M40" s="126"/>
-      <c r="N40" s="126"/>
-      <c r="O40" s="127"/>
-      <c r="P40" s="61" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q40" s="62" t="s">
-        <v>152</v>
-      </c>
-      <c r="R40" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="S40" s="63" t="s">
-        <v>154</v>
+      <c r="K40" s="73"/>
+      <c r="L40" s="96"/>
+      <c r="M40" s="97"/>
+      <c r="N40" s="97"/>
+      <c r="O40" s="98"/>
+      <c r="P40" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q40" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="R40" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="S40" s="62" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="114" t="s">
-        <v>155</v>
-      </c>
-      <c r="B41" s="115"/>
-      <c r="C41" s="116" t="s">
-        <v>191</v>
-      </c>
-      <c r="D41" s="117"/>
-      <c r="E41" s="117"/>
-      <c r="F41" s="117"/>
-      <c r="G41" s="118"/>
+      <c r="A41" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="86"/>
+      <c r="C41" s="87" t="s">
+        <v>183</v>
+      </c>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="89"/>
       <c r="H41" s="39" t="s">
         <v>41</v>
       </c>
@@ -7571,26 +8043,39 @@
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Turno  que se quiere dar de baja.</v>
       </c>
-      <c r="K41" s="184"/>
-      <c r="L41" s="119"/>
-      <c r="M41" s="120"/>
-      <c r="N41" s="120"/>
-      <c r="O41" s="121"/>
+      <c r="K41" s="74"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="91"/>
+      <c r="N41" s="91"/>
+      <c r="O41" s="92"/>
       <c r="P41" s="25" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="Q41" s="41" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="R41" s="41" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="S41" s="41" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:G36"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="P35:Q35"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="L41:O41"/>
@@ -7606,19 +8091,6 @@
     <mergeCell ref="H37:H38"/>
     <mergeCell ref="J37:J38"/>
     <mergeCell ref="L37:O38"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="C35:G36"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="P35:Q35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{94AC8755-4E69-45C0-81AE-103982376658}"/>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Reservas.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Reservas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AC1D78-FA01-4D4A-920C-F6611F31C884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F613D29-4108-4381-8FFC-78D572ACC29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{9E75F319-B909-453D-9AFC-FA9C5B40B20E}"/>
   </bookViews>
@@ -3082,6 +3082,114 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3223,113 +3331,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3361,17 +3373,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3381,12 +3387,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3997,73 +3997,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="162" t="str">
+      <c r="B2" s="95" t="str">
         <f>'Listado Objetos de Dominio'!A3</f>
         <v>Reserva</v>
       </c>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="163" t="str">
+      <c r="B3" s="96" t="str">
         <f>'Listado Objetos de Dominio'!B3</f>
         <v>Corresponde a cada una de las reservas que pude hacer el residente, es decir, el residente puede reservar una zona común, ejemplo: El residente 001 reserva la piscina con su respectivo turno.</v>
       </c>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="163"/>
-      <c r="P3" s="163"/>
-      <c r="Q3" s="163"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -4331,11 +4331,11 @@
     </row>
     <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="158" t="s">
+      <c r="A10" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="159"/>
-      <c r="C10" s="160"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="93"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
@@ -4349,10 +4349,10 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="164" t="s">
+      <c r="A12" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="166" t="s">
+      <c r="B12" s="99" t="s">
         <v>88</v>
       </c>
       <c r="C12" s="30" t="s">
@@ -4360,54 +4360,54 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="165"/>
-      <c r="B13" s="167"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="100"/>
       <c r="C13" s="31" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="150" t="s">
+      <c r="B15" s="114"/>
+      <c r="C15" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="151"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="147"/>
-      <c r="H15" s="143" t="s">
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="144"/>
-      <c r="J15" s="145"/>
-      <c r="K15" s="143" t="s">
+      <c r="I15" s="112"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="145"/>
-      <c r="P15" s="143" t="s">
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="86"/>
+      <c r="P15" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="Q15" s="145"/>
-      <c r="R15" s="143" t="s">
+      <c r="Q15" s="86"/>
+      <c r="R15" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="S15" s="154"/>
+      <c r="S15" s="87"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="148"/>
-      <c r="B16" s="149"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="153"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="153"/>
-      <c r="G16" s="149"/>
+      <c r="A16" s="115"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="116"/>
       <c r="H16" s="45" t="s">
         <v>54</v>
       </c>
@@ -4420,12 +4420,12 @@
       <c r="K16" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="155" t="s">
+      <c r="L16" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="M16" s="156"/>
-      <c r="N16" s="156"/>
-      <c r="O16" s="157"/>
+      <c r="M16" s="89"/>
+      <c r="N16" s="89"/>
+      <c r="O16" s="90"/>
       <c r="P16" s="32" t="s">
         <v>56</v>
       </c>
@@ -4440,34 +4440,34 @@
       </c>
     </row>
     <row r="17" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="135" t="s">
+      <c r="A17" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="112" t="s">
+      <c r="B17" s="105"/>
+      <c r="C17" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="93" t="str">
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="129" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I17" s="141" t="str">
+      <c r="I17" s="110" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
-      <c r="J17" s="93" t="str">
+      <c r="J17" s="129" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",$B$2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Reserva</v>
       </c>
       <c r="K17" s="46"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="123"/>
+      <c r="L17" s="157"/>
+      <c r="M17" s="158"/>
+      <c r="N17" s="158"/>
+      <c r="O17" s="159"/>
       <c r="P17" s="14" t="s">
         <v>158</v>
       </c>
@@ -4482,21 +4482,21 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="137"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="142"/>
-      <c r="J18" s="94"/>
+      <c r="A18" s="106"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="152"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="130"/>
       <c r="K18" s="54"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="125"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="126"/>
+      <c r="L18" s="160"/>
+      <c r="M18" s="161"/>
+      <c r="N18" s="161"/>
+      <c r="O18" s="162"/>
       <c r="P18" s="14" t="s">
         <v>159</v>
       </c>
@@ -4511,21 +4511,21 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="137"/>
-      <c r="B19" s="138"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="94"/>
+      <c r="A19" s="106"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="130"/>
       <c r="K19" s="54"/>
-      <c r="L19" s="124"/>
-      <c r="M19" s="125"/>
-      <c r="N19" s="125"/>
-      <c r="O19" s="126"/>
+      <c r="L19" s="160"/>
+      <c r="M19" s="161"/>
+      <c r="N19" s="161"/>
+      <c r="O19" s="162"/>
       <c r="P19" s="14" t="s">
         <v>160</v>
       </c>
@@ -4540,21 +4540,21 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="137"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="142"/>
-      <c r="J20" s="94"/>
+      <c r="A20" s="106"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="152"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="130"/>
       <c r="K20" s="54"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="125"/>
-      <c r="N20" s="125"/>
-      <c r="O20" s="126"/>
+      <c r="L20" s="160"/>
+      <c r="M20" s="161"/>
+      <c r="N20" s="161"/>
+      <c r="O20" s="162"/>
       <c r="P20" s="14" t="s">
         <v>161</v>
       </c>
@@ -4569,16 +4569,16 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="139"/>
-      <c r="B21" s="140"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="95"/>
+      <c r="A21" s="108"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="154"/>
+      <c r="D21" s="155"/>
+      <c r="E21" s="155"/>
+      <c r="F21" s="155"/>
+      <c r="G21" s="156"/>
+      <c r="H21" s="131"/>
       <c r="I21" s="52"/>
-      <c r="J21" s="95"/>
+      <c r="J21" s="131"/>
       <c r="K21" s="54"/>
       <c r="L21" s="55"/>
       <c r="M21" s="56"/>
@@ -4598,17 +4598,17 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="127" t="s">
+      <c r="A22" s="163" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="128"/>
-      <c r="C22" s="129" t="s">
+      <c r="B22" s="164"/>
+      <c r="C22" s="165" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="131"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="167"/>
       <c r="H22" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
@@ -4624,12 +4624,12 @@
       <c r="K22" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="L22" s="132" t="s">
+      <c r="L22" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="M22" s="133"/>
-      <c r="N22" s="133"/>
-      <c r="O22" s="134"/>
+      <c r="M22" s="102"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="103"/>
       <c r="P22" s="23" t="s">
         <v>163</v>
       </c>
@@ -4644,34 +4644,34 @@
       </c>
     </row>
     <row r="23" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="108" t="s">
+      <c r="A23" s="144" t="s">
         <v>141</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="96" t="s">
+      <c r="B23" s="145"/>
+      <c r="C23" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="97"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="104" t="str">
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="140" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosReserva</v>
       </c>
-      <c r="I23" s="106" t="str">
+      <c r="I23" s="142" t="str">
         <f>B2</f>
         <v>Reserva</v>
       </c>
-      <c r="J23" s="104" t="str">
+      <c r="J23" s="140" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar de la ",$B$2)</f>
         <v>Corresponde a los datos que se van a modificar de la Reserva</v>
       </c>
-      <c r="K23" s="102"/>
-      <c r="L23" s="96"/>
-      <c r="M23" s="97"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="98"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="132"/>
+      <c r="M23" s="133"/>
+      <c r="N23" s="133"/>
+      <c r="O23" s="134"/>
       <c r="P23" s="60" t="s">
         <v>164</v>
       </c>
@@ -4686,21 +4686,21 @@
       </c>
     </row>
     <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="110"/>
-      <c r="B24" s="111"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="103"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="100"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="101"/>
+      <c r="A24" s="146"/>
+      <c r="B24" s="147"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="136"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="141"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="135"/>
+      <c r="M24" s="136"/>
+      <c r="N24" s="136"/>
+      <c r="O24" s="137"/>
       <c r="P24" s="60" t="s">
         <v>161</v>
       </c>
@@ -4715,17 +4715,17 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="85" t="s">
+      <c r="A25" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="B25" s="86"/>
-      <c r="C25" s="87" t="s">
+      <c r="B25" s="122"/>
+      <c r="C25" s="123" t="s">
         <v>179</v>
       </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="89"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="125"/>
       <c r="H25" s="39" t="s">
         <v>41</v>
       </c>
@@ -4737,10 +4737,10 @@
         <v>Corresponde al identificador de la Reserva  que se quiere dar de baja.</v>
       </c>
       <c r="K25" s="40"/>
-      <c r="L25" s="90"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="92"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="128"/>
       <c r="P25" s="25" t="s">
         <v>164</v>
       </c>
@@ -4756,22 +4756,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="A17:B21"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:G16"/>
-    <mergeCell ref="H15:J15"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="L25:O25"/>
@@ -4788,6 +4772,22 @@
     <mergeCell ref="L17:O20"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:G22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="A17:B21"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="K15:O15"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:G16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -4845,73 +4845,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="162" t="str">
+      <c r="B2" s="95" t="str">
         <f>'Listado Objetos de Dominio'!A5</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="163" t="str">
+      <c r="B3" s="96" t="str">
         <f>'Listado Objetos de Dominio'!B5</f>
         <v>Corresponde a la persona que puede realizar una reserva para una zona común.</v>
       </c>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="163"/>
-      <c r="P3" s="163"/>
-      <c r="Q3" s="163"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -5928,21 +5928,21 @@
     </row>
     <row r="24" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="181" t="s">
+      <c r="A25" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="181"/>
-      <c r="C25" s="181"/>
-      <c r="E25" s="181" t="s">
+      <c r="B25" s="168"/>
+      <c r="C25" s="168"/>
+      <c r="E25" s="168" t="s">
         <v>109</v>
       </c>
-      <c r="F25" s="181"/>
-      <c r="G25" s="181"/>
-      <c r="I25" s="181" t="s">
+      <c r="F25" s="168"/>
+      <c r="G25" s="168"/>
+      <c r="I25" s="168" t="s">
         <v>46</v>
       </c>
-      <c r="J25" s="181"/>
-      <c r="K25" s="181"/>
+      <c r="J25" s="168"/>
+      <c r="K25" s="168"/>
     </row>
     <row r="26" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
@@ -5974,113 +5974,113 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="179" t="s">
+      <c r="A27" s="169" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="180" t="s">
+      <c r="B27" s="170" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="178" t="s">
+      <c r="C27" s="171" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="180" t="s">
+      <c r="E27" s="170" t="s">
         <v>112</v>
       </c>
-      <c r="F27" s="180" t="s">
+      <c r="F27" s="170" t="s">
         <v>113</v>
       </c>
-      <c r="G27" s="178" t="s">
+      <c r="G27" s="171" t="s">
         <v>101</v>
       </c>
       <c r="H27" s="43"/>
-      <c r="I27" s="179" t="s">
+      <c r="I27" s="169" t="s">
         <v>114</v>
       </c>
-      <c r="J27" s="180" t="s">
+      <c r="J27" s="170" t="s">
         <v>115</v>
       </c>
-      <c r="K27" s="178" t="s">
+      <c r="K27" s="171" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="179"/>
-      <c r="B28" s="180"/>
-      <c r="C28" s="178"/>
-      <c r="E28" s="180"/>
-      <c r="F28" s="180"/>
-      <c r="G28" s="178"/>
+      <c r="A28" s="169"/>
+      <c r="B28" s="170"/>
+      <c r="C28" s="171"/>
+      <c r="E28" s="170"/>
+      <c r="F28" s="170"/>
+      <c r="G28" s="171"/>
       <c r="H28" s="43"/>
-      <c r="I28" s="179"/>
-      <c r="J28" s="180"/>
-      <c r="K28" s="178"/>
+      <c r="I28" s="169"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="171"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="179"/>
-      <c r="B29" s="180"/>
-      <c r="C29" s="178" t="s">
+      <c r="A29" s="169"/>
+      <c r="B29" s="170"/>
+      <c r="C29" s="171" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="180"/>
-      <c r="F29" s="180"/>
-      <c r="G29" s="178"/>
-      <c r="I29" s="179"/>
-      <c r="J29" s="180"/>
-      <c r="K29" s="178"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="171"/>
+      <c r="I29" s="169"/>
+      <c r="J29" s="170"/>
+      <c r="K29" s="171"/>
     </row>
     <row r="30" spans="1:21" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="179"/>
-      <c r="B30" s="180"/>
-      <c r="C30" s="178"/>
-      <c r="E30" s="180"/>
-      <c r="F30" s="180"/>
-      <c r="G30" s="178"/>
-      <c r="I30" s="179"/>
-      <c r="J30" s="180"/>
-      <c r="K30" s="178"/>
+      <c r="A30" s="169"/>
+      <c r="B30" s="170"/>
+      <c r="C30" s="171"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="170"/>
+      <c r="G30" s="171"/>
+      <c r="I30" s="169"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="171"/>
     </row>
     <row r="31" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A32" s="146" t="s">
+      <c r="A32" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="147"/>
-      <c r="C32" s="150" t="s">
+      <c r="B32" s="114"/>
+      <c r="C32" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="151"/>
-      <c r="E32" s="151"/>
-      <c r="F32" s="151"/>
-      <c r="G32" s="147"/>
-      <c r="H32" s="143" t="s">
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="144"/>
-      <c r="J32" s="145"/>
-      <c r="K32" s="143" t="s">
+      <c r="I32" s="112"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="L32" s="144"/>
-      <c r="M32" s="144"/>
-      <c r="N32" s="144"/>
-      <c r="O32" s="145"/>
-      <c r="P32" s="143" t="s">
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="86"/>
+      <c r="P32" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="Q32" s="145"/>
-      <c r="R32" s="143" t="s">
+      <c r="Q32" s="86"/>
+      <c r="R32" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="S32" s="154"/>
+      <c r="S32" s="87"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="148"/>
-      <c r="B33" s="149"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="149"/>
+      <c r="A33" s="115"/>
+      <c r="B33" s="116"/>
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="116"/>
       <c r="H33" s="45" t="s">
         <v>54</v>
       </c>
@@ -6093,12 +6093,12 @@
       <c r="K33" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L33" s="155" t="s">
+      <c r="L33" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="156"/>
-      <c r="N33" s="156"/>
-      <c r="O33" s="157"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="89"/>
+      <c r="O33" s="90"/>
       <c r="P33" s="32" t="s">
         <v>56</v>
       </c>
@@ -6113,34 +6113,34 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="135" t="s">
+      <c r="A34" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="136"/>
-      <c r="C34" s="112" t="s">
+      <c r="B34" s="105"/>
+      <c r="C34" s="148" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="113"/>
-      <c r="E34" s="113"/>
-      <c r="F34" s="113"/>
-      <c r="G34" s="114"/>
-      <c r="H34" s="93" t="str">
+      <c r="D34" s="149"/>
+      <c r="E34" s="149"/>
+      <c r="F34" s="149"/>
+      <c r="G34" s="150"/>
+      <c r="H34" s="129" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I34" s="141" t="str">
+      <c r="I34" s="110" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J34" s="176" t="str">
+      <c r="J34" s="180" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Residente</v>
       </c>
       <c r="K34" s="46"/>
-      <c r="L34" s="121"/>
-      <c r="M34" s="122"/>
-      <c r="N34" s="122"/>
-      <c r="O34" s="123"/>
+      <c r="L34" s="157"/>
+      <c r="M34" s="158"/>
+      <c r="N34" s="158"/>
+      <c r="O34" s="159"/>
       <c r="P34" s="14" t="s">
         <v>118</v>
       </c>
@@ -6155,21 +6155,21 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="137"/>
-      <c r="B35" s="138"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="117"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="142"/>
-      <c r="J35" s="177"/>
+      <c r="A35" s="106"/>
+      <c r="B35" s="107"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="153"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="111"/>
+      <c r="J35" s="181"/>
       <c r="K35" s="54"/>
-      <c r="L35" s="124"/>
-      <c r="M35" s="125"/>
-      <c r="N35" s="125"/>
-      <c r="O35" s="126"/>
+      <c r="L35" s="160"/>
+      <c r="M35" s="161"/>
+      <c r="N35" s="161"/>
+      <c r="O35" s="162"/>
       <c r="P35" s="14" t="s">
         <v>122</v>
       </c>
@@ -6184,21 +6184,21 @@
       </c>
     </row>
     <row r="36" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="137"/>
-      <c r="B36" s="138"/>
-      <c r="C36" s="115"/>
-      <c r="D36" s="116"/>
-      <c r="E36" s="116"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="142"/>
-      <c r="J36" s="177"/>
+      <c r="A36" s="106"/>
+      <c r="B36" s="107"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="152"/>
+      <c r="G36" s="153"/>
+      <c r="H36" s="130"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="181"/>
       <c r="K36" s="54"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="125"/>
-      <c r="N36" s="125"/>
-      <c r="O36" s="126"/>
+      <c r="L36" s="160"/>
+      <c r="M36" s="161"/>
+      <c r="N36" s="161"/>
+      <c r="O36" s="162"/>
       <c r="P36" s="14" t="s">
         <v>125</v>
       </c>
@@ -6213,21 +6213,21 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="137"/>
-      <c r="B37" s="138"/>
-      <c r="C37" s="115"/>
-      <c r="D37" s="116"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="142"/>
-      <c r="J37" s="177"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="151"/>
+      <c r="D37" s="152"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="153"/>
+      <c r="H37" s="130"/>
+      <c r="I37" s="111"/>
+      <c r="J37" s="181"/>
       <c r="K37" s="54"/>
-      <c r="L37" s="124"/>
-      <c r="M37" s="125"/>
-      <c r="N37" s="125"/>
-      <c r="O37" s="126"/>
+      <c r="L37" s="160"/>
+      <c r="M37" s="161"/>
+      <c r="N37" s="161"/>
+      <c r="O37" s="162"/>
       <c r="P37" s="14" t="s">
         <v>129</v>
       </c>
@@ -6242,8 +6242,8 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="139"/>
-      <c r="B38" s="140"/>
+      <c r="A38" s="108"/>
+      <c r="B38" s="109"/>
       <c r="C38" s="48"/>
       <c r="D38" s="49"/>
       <c r="E38" s="49"/>
@@ -6271,17 +6271,17 @@
       </c>
     </row>
     <row r="39" spans="1:19" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="127" t="s">
+      <c r="A39" s="163" t="s">
         <v>136</v>
       </c>
-      <c r="B39" s="128"/>
-      <c r="C39" s="129" t="s">
+      <c r="B39" s="164"/>
+      <c r="C39" s="165" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="130"/>
-      <c r="E39" s="130"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="131"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="167"/>
       <c r="H39" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
@@ -6297,12 +6297,12 @@
       <c r="K39" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="L39" s="132" t="s">
+      <c r="L39" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="M39" s="133"/>
-      <c r="N39" s="133"/>
-      <c r="O39" s="134"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="102"/>
+      <c r="O39" s="103"/>
       <c r="P39" s="23" t="s">
         <v>139</v>
       </c>
@@ -6317,17 +6317,17 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="168" t="s">
+      <c r="A40" s="172" t="s">
         <v>141</v>
       </c>
-      <c r="B40" s="169"/>
-      <c r="C40" s="170" t="s">
+      <c r="B40" s="173"/>
+      <c r="C40" s="174" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="171"/>
-      <c r="E40" s="171"/>
-      <c r="F40" s="171"/>
-      <c r="G40" s="172"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="175"/>
+      <c r="F40" s="175"/>
+      <c r="G40" s="176"/>
       <c r="H40" s="36" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
@@ -6341,10 +6341,10 @@
         <v>Corresponde a los datos que se van a modificar del Residente</v>
       </c>
       <c r="K40" s="38"/>
-      <c r="L40" s="173"/>
-      <c r="M40" s="174"/>
-      <c r="N40" s="174"/>
-      <c r="O40" s="175"/>
+      <c r="L40" s="177"/>
+      <c r="M40" s="178"/>
+      <c r="N40" s="178"/>
+      <c r="O40" s="179"/>
       <c r="P40" s="60" t="s">
         <v>143</v>
       </c>
@@ -6359,17 +6359,17 @@
       </c>
     </row>
     <row r="41" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="85" t="s">
+      <c r="A41" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="86"/>
-      <c r="C41" s="87" t="s">
+      <c r="B41" s="122"/>
+      <c r="C41" s="123" t="s">
         <v>148</v>
       </c>
-      <c r="D41" s="88"/>
-      <c r="E41" s="88"/>
-      <c r="F41" s="88"/>
-      <c r="G41" s="89"/>
+      <c r="D41" s="124"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="124"/>
+      <c r="G41" s="125"/>
       <c r="H41" s="39" t="s">
         <v>41</v>
       </c>
@@ -6381,10 +6381,10 @@
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
       <c r="K41" s="40"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="91"/>
-      <c r="N41" s="91"/>
-      <c r="O41" s="92"/>
+      <c r="L41" s="126"/>
+      <c r="M41" s="127"/>
+      <c r="N41" s="127"/>
+      <c r="O41" s="128"/>
       <c r="P41" s="25" t="s">
         <v>143</v>
       </c>
@@ -6400,29 +6400,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="G27:G30"/>
-    <mergeCell ref="I27:I30"/>
-    <mergeCell ref="J27:J30"/>
-    <mergeCell ref="K27:K30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="A32:B33"/>
-    <mergeCell ref="C32:G33"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="K32:O32"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="L41:O41"/>
@@ -6438,6 +6415,29 @@
     <mergeCell ref="I34:I37"/>
     <mergeCell ref="J34:J37"/>
     <mergeCell ref="L34:O37"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="C32:G33"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="K32:O32"/>
+    <mergeCell ref="G27:G30"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="J27:J30"/>
+    <mergeCell ref="K27:K30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="F27:F30"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="I25:K25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{1AE4FE85-AF13-4BAA-9ECE-73FAE508027B}"/>
@@ -6496,73 +6496,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="162" t="str">
+      <c r="B2" s="95" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Turno</v>
       </c>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="163" t="str">
+      <c r="B3" s="96" t="str">
         <f>'Listado Objetos de Dominio'!B4</f>
         <v>Corresponde a los turnos que un residente puede reservar en una agenda, es decir, el residente toma un turno que esta disponible de una agenda que anteriormente ya esta programada.</v>
       </c>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="163"/>
-      <c r="P3" s="163"/>
-      <c r="Q3" s="163"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -7740,11 +7740,11 @@
     </row>
     <row r="27" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="158" t="s">
+      <c r="A28" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="159"/>
-      <c r="C28" s="160"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="93"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
@@ -7758,10 +7758,10 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="164" t="s">
+      <c r="A30" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="166" t="s">
+      <c r="B30" s="99" t="s">
         <v>90</v>
       </c>
       <c r="C30" s="30" t="s">
@@ -7769,68 +7769,68 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="185"/>
-      <c r="B31" s="186"/>
+      <c r="A31" s="182"/>
+      <c r="B31" s="183"/>
       <c r="C31" s="30" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="185"/>
-      <c r="B32" s="186"/>
+      <c r="A32" s="182"/>
+      <c r="B32" s="183"/>
       <c r="C32" s="30" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="165"/>
-      <c r="B33" s="167"/>
+      <c r="A33" s="98"/>
+      <c r="B33" s="100"/>
       <c r="C33" s="42" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A35" s="146" t="s">
+      <c r="A35" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="147"/>
-      <c r="C35" s="150" t="s">
+      <c r="B35" s="114"/>
+      <c r="C35" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="147"/>
-      <c r="H35" s="143" t="s">
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="114"/>
+      <c r="H35" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="I35" s="144"/>
-      <c r="J35" s="145"/>
-      <c r="K35" s="143" t="s">
+      <c r="I35" s="112"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="L35" s="144"/>
-      <c r="M35" s="144"/>
-      <c r="N35" s="144"/>
-      <c r="O35" s="145"/>
-      <c r="P35" s="143" t="s">
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="Q35" s="145"/>
-      <c r="R35" s="143" t="s">
+      <c r="Q35" s="86"/>
+      <c r="R35" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="S35" s="154"/>
+      <c r="S35" s="87"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A36" s="148"/>
-      <c r="B36" s="149"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="153"/>
-      <c r="E36" s="153"/>
-      <c r="F36" s="153"/>
-      <c r="G36" s="149"/>
+      <c r="A36" s="115"/>
+      <c r="B36" s="116"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="116"/>
       <c r="H36" s="45" t="s">
         <v>54</v>
       </c>
@@ -7843,12 +7843,12 @@
       <c r="K36" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="L36" s="155" t="s">
+      <c r="L36" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="M36" s="156"/>
-      <c r="N36" s="156"/>
-      <c r="O36" s="157"/>
+      <c r="M36" s="89"/>
+      <c r="N36" s="89"/>
+      <c r="O36" s="90"/>
       <c r="P36" s="32" t="s">
         <v>56</v>
       </c>
@@ -7863,34 +7863,34 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="135" t="s">
+      <c r="A37" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="136"/>
-      <c r="C37" s="112" t="s">
+      <c r="B37" s="105"/>
+      <c r="C37" s="148" t="s">
         <v>180</v>
       </c>
-      <c r="D37" s="113"/>
-      <c r="E37" s="113"/>
-      <c r="F37" s="113"/>
-      <c r="G37" s="114"/>
-      <c r="H37" s="93" t="str">
+      <c r="D37" s="149"/>
+      <c r="E37" s="149"/>
+      <c r="F37" s="149"/>
+      <c r="G37" s="150"/>
+      <c r="H37" s="129" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
       </c>
-      <c r="I37" s="93" t="str">
+      <c r="I37" s="129" t="str">
         <f>B2</f>
         <v>Turno</v>
       </c>
-      <c r="J37" s="93" t="str">
+      <c r="J37" s="129" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",$B$2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Turno</v>
       </c>
       <c r="K37" s="71"/>
-      <c r="L37" s="121"/>
-      <c r="M37" s="122"/>
-      <c r="N37" s="122"/>
-      <c r="O37" s="123"/>
+      <c r="L37" s="157"/>
+      <c r="M37" s="158"/>
+      <c r="N37" s="158"/>
+      <c r="O37" s="159"/>
       <c r="P37" s="14" t="s">
         <v>158</v>
       </c>
@@ -7905,21 +7905,21 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="137"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="115"/>
-      <c r="D38" s="116"/>
-      <c r="E38" s="116"/>
-      <c r="F38" s="116"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="94"/>
-      <c r="J38" s="94"/>
+      <c r="A38" s="106"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="151"/>
+      <c r="D38" s="152"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="152"/>
+      <c r="G38" s="153"/>
+      <c r="H38" s="130"/>
+      <c r="I38" s="130"/>
+      <c r="J38" s="130"/>
       <c r="K38" s="72"/>
-      <c r="L38" s="124"/>
-      <c r="M38" s="125"/>
-      <c r="N38" s="125"/>
-      <c r="O38" s="126"/>
+      <c r="L38" s="160"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="162"/>
       <c r="P38" s="14" t="s">
         <v>159</v>
       </c>
@@ -7934,17 +7934,17 @@
       </c>
     </row>
     <row r="39" spans="1:19" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="127" t="s">
+      <c r="A39" s="163" t="s">
         <v>136</v>
       </c>
-      <c r="B39" s="128"/>
-      <c r="C39" s="129" t="s">
+      <c r="B39" s="164"/>
+      <c r="C39" s="165" t="s">
         <v>181</v>
       </c>
-      <c r="D39" s="130"/>
-      <c r="E39" s="130"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="131"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="167"/>
       <c r="H39" s="34" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
@@ -7960,12 +7960,12 @@
       <c r="K39" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="L39" s="132" t="s">
+      <c r="L39" s="101" t="s">
         <v>186</v>
       </c>
-      <c r="M39" s="133"/>
-      <c r="N39" s="133"/>
-      <c r="O39" s="134"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="102"/>
+      <c r="O39" s="103"/>
       <c r="P39" s="23" t="s">
         <v>160</v>
       </c>
@@ -7980,17 +7980,17 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="108" t="s">
+      <c r="A40" s="144" t="s">
         <v>141</v>
       </c>
-      <c r="B40" s="109"/>
-      <c r="C40" s="182" t="s">
+      <c r="B40" s="145"/>
+      <c r="C40" s="184" t="s">
         <v>182</v>
       </c>
-      <c r="D40" s="183"/>
-      <c r="E40" s="183"/>
-      <c r="F40" s="183"/>
-      <c r="G40" s="184"/>
+      <c r="D40" s="185"/>
+      <c r="E40" s="185"/>
+      <c r="F40" s="185"/>
+      <c r="G40" s="186"/>
       <c r="H40" s="69" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTurno</v>
@@ -8004,10 +8004,10 @@
         <v>Corresponde a los datos que se van a modificar del Turno</v>
       </c>
       <c r="K40" s="73"/>
-      <c r="L40" s="96"/>
-      <c r="M40" s="97"/>
-      <c r="N40" s="97"/>
-      <c r="O40" s="98"/>
+      <c r="L40" s="132"/>
+      <c r="M40" s="133"/>
+      <c r="N40" s="133"/>
+      <c r="O40" s="134"/>
       <c r="P40" s="60" t="s">
         <v>161</v>
       </c>
@@ -8022,17 +8022,17 @@
       </c>
     </row>
     <row r="41" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="85" t="s">
+      <c r="A41" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="86"/>
-      <c r="C41" s="87" t="s">
+      <c r="B41" s="122"/>
+      <c r="C41" s="123" t="s">
         <v>183</v>
       </c>
-      <c r="D41" s="88"/>
-      <c r="E41" s="88"/>
-      <c r="F41" s="88"/>
-      <c r="G41" s="89"/>
+      <c r="D41" s="124"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="124"/>
+      <c r="G41" s="125"/>
       <c r="H41" s="39" t="s">
         <v>41</v>
       </c>
@@ -8044,10 +8044,10 @@
         <v>Corresponde al identificador del Turno  que se quiere dar de baja.</v>
       </c>
       <c r="K41" s="74"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="91"/>
-      <c r="N41" s="91"/>
-      <c r="O41" s="92"/>
+      <c r="L41" s="126"/>
+      <c r="M41" s="127"/>
+      <c r="N41" s="127"/>
+      <c r="O41" s="128"/>
       <c r="P41" s="25" t="s">
         <v>161</v>
       </c>
@@ -8063,19 +8063,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="C35:G36"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="P35:Q35"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="L41:O41"/>
@@ -8091,6 +8078,19 @@
     <mergeCell ref="H37:H38"/>
     <mergeCell ref="J37:J38"/>
     <mergeCell ref="L37:O38"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:G36"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="P35:Q35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{94AC8755-4E69-45C0-81AE-103982376658}"/>
